--- a/expenses.xlsx
+++ b/expenses.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11940"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Expenses" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Ilyas" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="burhanuddin" state="visible" r:id="rId6"/>
+    <sheet name="Expenses" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1059" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1028" uniqueCount="260">
   <si>
     <t>srNo</t>
   </si>
@@ -51,9 +52,6 @@
     <t>Cash</t>
   </si>
   <si>
-    <t>No description provided</t>
-  </si>
-  <si>
     <t>Niyaz 29</t>
   </si>
   <si>
@@ -789,52 +787,13 @@
     <t>29300.00</t>
   </si>
   <si>
-    <t>2026-04-23</t>
+    <t>2026-04-27</t>
   </si>
   <si>
     <t>0.00</t>
   </si>
   <si>
     <t>Pending</t>
-  </si>
-  <si>
-    <t>Sr No</t>
-  </si>
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>Given To</t>
-  </si>
-  <si>
-    <t>Amount</t>
-  </si>
-  <si>
-    <t>Mode</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>Fund</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>2026-04-26</t>
-  </si>
-  <si>
-    <t>Ambalal khatik</t>
-  </si>
-  <si>
-    <t>565.00</t>
-  </si>
-  <si>
-    <t>Test</t>
-  </si>
-  <si>
-    <t>787.00</t>
   </si>
 </sst>
 </file>
@@ -843,11 +802,11 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -900,44 +859,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线 Light"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -967,12 +926,12 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -1011,210 +970,151 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="35000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="100000"/>
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
                 <a:shade val="100000"/>
-                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:shade val="100000"/>
-                <a:satMod val="350000"/>
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
+                <a:alpha val="63000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="40000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:spDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="3">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </a:style>
-    </a:spDef>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H190"/>
-  <sheetFormatPr defaultRowHeight="0" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="0" customHeight="1" zeroHeight="1" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1240,7 +1140,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1256,17 +1156,14 @@
       <c r="E2" t="s">
         <v>11</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>12</v>
       </c>
-      <c r="G2" t="s">
-        <v>13</v>
-      </c>
       <c r="H2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1277,19 +1174,19 @@
         <v>9</v>
       </c>
       <c r="D3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" t="s">
         <v>15</v>
       </c>
-      <c r="E3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3" t="s">
-        <v>16</v>
-      </c>
       <c r="H3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1297,22 +1194,22 @@
         <v>8</v>
       </c>
       <c r="C4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" t="s">
         <v>17</v>
       </c>
-      <c r="D4" t="s">
-        <v>18</v>
-      </c>
       <c r="E4" t="s">
         <v>11</v>
       </c>
       <c r="G4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1320,22 +1217,22 @@
         <v>8</v>
       </c>
       <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
         <v>19</v>
       </c>
-      <c r="D5" t="s">
-        <v>20</v>
-      </c>
       <c r="E5" t="s">
         <v>11</v>
       </c>
       <c r="G5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1343,22 +1240,22 @@
         <v>8</v>
       </c>
       <c r="C6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E6" t="s">
         <v>11</v>
       </c>
       <c r="G6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1366,22 +1263,22 @@
         <v>8</v>
       </c>
       <c r="C7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" t="s">
         <v>22</v>
       </c>
-      <c r="D7" t="s">
-        <v>23</v>
-      </c>
       <c r="E7" t="s">
         <v>11</v>
       </c>
       <c r="G7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1389,4007 +1286,3866 @@
         <v>8</v>
       </c>
       <c r="C8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" t="s">
         <v>24</v>
       </c>
-      <c r="D8" t="s">
-        <v>25</v>
-      </c>
       <c r="E8" t="s">
         <v>11</v>
       </c>
       <c r="G8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" t="s">
         <v>26</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9" t="s">
+        <v>11</v>
+      </c>
+      <c r="G9" t="s">
         <v>27</v>
       </c>
-      <c r="D9" t="s">
-        <v>20</v>
-      </c>
-      <c r="E9" t="s">
-        <v>11</v>
-      </c>
-      <c r="G9" t="s">
-        <v>28</v>
-      </c>
       <c r="H9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" t="s">
         <v>29</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>30</v>
       </c>
-      <c r="D10" t="s">
-        <v>31</v>
-      </c>
       <c r="E10" t="s">
         <v>11</v>
       </c>
       <c r="G10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H10" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E11" t="s">
         <v>11</v>
       </c>
       <c r="G11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H11" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" t="s">
         <v>32</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>33</v>
       </c>
-      <c r="D12" t="s">
-        <v>34</v>
-      </c>
       <c r="E12" t="s">
         <v>11</v>
       </c>
       <c r="G12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C13" t="s">
+        <v>34</v>
+      </c>
+      <c r="D13" t="s">
         <v>35</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
+        <v>11</v>
+      </c>
+      <c r="G13" t="s">
+        <v>27</v>
+      </c>
+      <c r="H13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" t="s">
         <v>36</v>
       </c>
-      <c r="E13" t="s">
-        <v>11</v>
-      </c>
-      <c r="G13" t="s">
-        <v>28</v>
-      </c>
-      <c r="H13" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14">
-        <v>13</v>
-      </c>
-      <c r="B14" t="s">
-        <v>32</v>
-      </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>37</v>
       </c>
-      <c r="D14" t="s">
-        <v>38</v>
-      </c>
       <c r="E14" t="s">
         <v>11</v>
       </c>
       <c r="G14" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H14" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C15" t="s">
+        <v>38</v>
+      </c>
+      <c r="D15" t="s">
         <v>39</v>
       </c>
-      <c r="D15" t="s">
-        <v>40</v>
-      </c>
       <c r="E15" t="s">
         <v>11</v>
       </c>
       <c r="G15" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H15" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C16" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D16" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E16" t="s">
         <v>11</v>
       </c>
       <c r="G16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H16" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="s">
+        <v>41</v>
+      </c>
+      <c r="C17" t="s">
+        <v>40</v>
+      </c>
+      <c r="D17" t="s">
         <v>42</v>
       </c>
-      <c r="C17" t="s">
-        <v>41</v>
-      </c>
-      <c r="D17" t="s">
-        <v>43</v>
-      </c>
       <c r="E17" t="s">
         <v>11</v>
       </c>
       <c r="G17" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H17" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C18" t="s">
+        <v>43</v>
+      </c>
+      <c r="D18" t="s">
         <v>44</v>
       </c>
-      <c r="D18" t="s">
-        <v>45</v>
-      </c>
       <c r="E18" t="s">
         <v>11</v>
       </c>
       <c r="G18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H18" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C19" t="s">
+        <v>45</v>
+      </c>
+      <c r="D19" t="s">
         <v>46</v>
       </c>
-      <c r="D19" t="s">
-        <v>47</v>
-      </c>
       <c r="E19" t="s">
         <v>11</v>
       </c>
       <c r="G19" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H19" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C20" t="s">
+        <v>47</v>
+      </c>
+      <c r="D20" t="s">
         <v>48</v>
       </c>
-      <c r="D20" t="s">
-        <v>49</v>
-      </c>
       <c r="E20" t="s">
         <v>11</v>
       </c>
       <c r="G20" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H20" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" t="s">
+        <v>49</v>
+      </c>
+      <c r="C21" t="s">
         <v>50</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D21" t="s">
         <v>51</v>
       </c>
-      <c r="D21" t="s">
-        <v>52</v>
-      </c>
       <c r="E21" t="s">
         <v>11</v>
       </c>
       <c r="G21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H21" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22" t="s">
+        <v>52</v>
+      </c>
+      <c r="C22" t="s">
         <v>53</v>
       </c>
-      <c r="C22" t="s">
+      <c r="D22" t="s">
         <v>54</v>
       </c>
-      <c r="D22" t="s">
+      <c r="E22" t="s">
+        <v>11</v>
+      </c>
+      <c r="G22" t="s">
         <v>55</v>
       </c>
-      <c r="E22" t="s">
-        <v>11</v>
-      </c>
-      <c r="G22" t="s">
-        <v>56</v>
-      </c>
       <c r="H22" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23" t="s">
+        <v>56</v>
+      </c>
+      <c r="C23" t="s">
         <v>57</v>
       </c>
-      <c r="C23" t="s">
+      <c r="D23" t="s">
         <v>58</v>
       </c>
-      <c r="D23" t="s">
-        <v>59</v>
-      </c>
       <c r="E23" t="s">
         <v>11</v>
       </c>
       <c r="G23" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H23" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C24" t="s">
+        <v>59</v>
+      </c>
+      <c r="D24" t="s">
         <v>60</v>
       </c>
-      <c r="D24" t="s">
-        <v>61</v>
-      </c>
       <c r="E24" t="s">
         <v>11</v>
       </c>
       <c r="G24" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25" t="s">
+        <v>61</v>
+      </c>
+      <c r="C25" t="s">
+        <v>40</v>
+      </c>
+      <c r="D25" t="s">
         <v>62</v>
       </c>
-      <c r="C25" t="s">
-        <v>41</v>
-      </c>
-      <c r="D25" t="s">
-        <v>63</v>
-      </c>
       <c r="E25" t="s">
         <v>11</v>
       </c>
       <c r="G25" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H25" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
       <c r="B26" t="s">
+        <v>63</v>
+      </c>
+      <c r="C26" t="s">
         <v>64</v>
       </c>
-      <c r="C26" t="s">
+      <c r="D26" t="s">
         <v>65</v>
       </c>
-      <c r="D26" t="s">
-        <v>66</v>
-      </c>
       <c r="E26" t="s">
         <v>11</v>
       </c>
       <c r="G26" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H26" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C27" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D27" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E27" t="s">
         <v>11</v>
       </c>
       <c r="G27" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H27" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C28" t="s">
+        <v>67</v>
+      </c>
+      <c r="D28" t="s">
         <v>68</v>
       </c>
-      <c r="D28" t="s">
-        <v>69</v>
-      </c>
       <c r="E28" t="s">
         <v>11</v>
       </c>
       <c r="G28" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H28" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
       <c r="B29" t="s">
+        <v>69</v>
+      </c>
+      <c r="C29" t="s">
         <v>70</v>
       </c>
-      <c r="C29" t="s">
+      <c r="D29" t="s">
         <v>71</v>
       </c>
-      <c r="D29" t="s">
-        <v>72</v>
-      </c>
       <c r="E29" t="s">
         <v>11</v>
       </c>
       <c r="G29" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H29" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C30" t="s">
+        <v>72</v>
+      </c>
+      <c r="D30" t="s">
         <v>73</v>
       </c>
-      <c r="D30" t="s">
+      <c r="E30" t="s">
         <v>74</v>
       </c>
-      <c r="E30" t="s">
+      <c r="G30" t="s">
         <v>75</v>
       </c>
-      <c r="G30" t="s">
-        <v>76</v>
-      </c>
       <c r="H30" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C31" t="s">
         <v>9</v>
       </c>
       <c r="D31" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E31" t="s">
         <v>11</v>
       </c>
       <c r="G31" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H31" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C32" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D32" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E32" t="s">
         <v>11</v>
       </c>
       <c r="G32" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H32" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
       <c r="B33" t="s">
+        <v>78</v>
+      </c>
+      <c r="C33" t="s">
         <v>79</v>
       </c>
-      <c r="C33" t="s">
+      <c r="D33" t="s">
         <v>80</v>
       </c>
-      <c r="D33" t="s">
+      <c r="E33" t="s">
+        <v>11</v>
+      </c>
+      <c r="G33" t="s">
         <v>81</v>
       </c>
-      <c r="E33" t="s">
-        <v>11</v>
-      </c>
-      <c r="G33" t="s">
-        <v>82</v>
-      </c>
       <c r="H33" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C34" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D34" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E34" t="s">
         <v>11</v>
       </c>
       <c r="G34" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H34" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C35" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D35" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E35" t="s">
         <v>11</v>
       </c>
       <c r="G35" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H35" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C36" t="s">
+        <v>84</v>
+      </c>
+      <c r="D36" t="s">
         <v>85</v>
       </c>
-      <c r="D36" t="s">
-        <v>86</v>
-      </c>
       <c r="E36" t="s">
         <v>11</v>
       </c>
       <c r="G36" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H36" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C37" t="s">
+        <v>86</v>
+      </c>
+      <c r="D37" t="s">
         <v>87</v>
       </c>
-      <c r="D37" t="s">
-        <v>88</v>
-      </c>
       <c r="E37" t="s">
         <v>11</v>
       </c>
       <c r="G37" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H37" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C38" t="s">
+        <v>88</v>
+      </c>
+      <c r="D38" t="s">
         <v>89</v>
       </c>
-      <c r="D38" t="s">
-        <v>90</v>
-      </c>
       <c r="E38" t="s">
         <v>11</v>
       </c>
       <c r="G38" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H38" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C39" t="s">
+        <v>90</v>
+      </c>
+      <c r="D39" t="s">
         <v>91</v>
       </c>
-      <c r="D39" t="s">
-        <v>92</v>
-      </c>
       <c r="E39" t="s">
         <v>11</v>
       </c>
       <c r="G39" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H39" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C40" t="s">
+        <v>92</v>
+      </c>
+      <c r="D40" t="s">
         <v>93</v>
       </c>
-      <c r="D40" t="s">
-        <v>94</v>
-      </c>
       <c r="E40" t="s">
         <v>11</v>
       </c>
       <c r="G40" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H40" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C41" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D41" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E41" t="s">
         <v>11</v>
       </c>
       <c r="G41" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H41" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>41</v>
       </c>
       <c r="B42" t="s">
+        <v>94</v>
+      </c>
+      <c r="C42" t="s">
         <v>95</v>
       </c>
-      <c r="C42" t="s">
+      <c r="D42" t="s">
         <v>96</v>
       </c>
-      <c r="D42" t="s">
-        <v>97</v>
-      </c>
       <c r="E42" t="s">
         <v>11</v>
       </c>
       <c r="G42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H42" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C43" t="s">
+        <v>97</v>
+      </c>
+      <c r="D43" t="s">
         <v>98</v>
       </c>
-      <c r="D43" t="s">
-        <v>99</v>
-      </c>
       <c r="E43" t="s">
         <v>11</v>
       </c>
       <c r="G43" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H43" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C44" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D44" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E44" t="s">
         <v>11</v>
       </c>
       <c r="G44" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H44" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C45" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D45" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E45" t="s">
         <v>11</v>
       </c>
       <c r="G45" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H45" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>45</v>
       </c>
       <c r="B46" t="s">
+        <v>101</v>
+      </c>
+      <c r="C46" t="s">
+        <v>38</v>
+      </c>
+      <c r="D46" t="s">
         <v>102</v>
       </c>
-      <c r="C46" t="s">
-        <v>39</v>
-      </c>
-      <c r="D46" t="s">
-        <v>103</v>
-      </c>
       <c r="E46" t="s">
         <v>11</v>
       </c>
       <c r="G46" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H46" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C47" t="s">
+        <v>103</v>
+      </c>
+      <c r="D47" t="s">
         <v>104</v>
       </c>
-      <c r="D47" t="s">
-        <v>105</v>
-      </c>
       <c r="E47" t="s">
         <v>11</v>
       </c>
       <c r="G47" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H47" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C48" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D48" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E48" t="s">
         <v>11</v>
       </c>
       <c r="G48" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H48" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C49" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D49" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E49" t="s">
         <v>11</v>
       </c>
       <c r="G49" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H49" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C50" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D50" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E50" t="s">
         <v>11</v>
       </c>
       <c r="G50" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H50" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C51" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D51" t="s">
+        <v>54</v>
+      </c>
+      <c r="E51" t="s">
+        <v>11</v>
+      </c>
+      <c r="G51" t="s">
         <v>55</v>
       </c>
-      <c r="E51" t="s">
-        <v>11</v>
-      </c>
-      <c r="G51" t="s">
-        <v>56</v>
-      </c>
       <c r="H51" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>51</v>
       </c>
       <c r="B52" t="s">
+        <v>107</v>
+      </c>
+      <c r="C52" t="s">
         <v>108</v>
       </c>
-      <c r="C52" t="s">
-        <v>109</v>
-      </c>
       <c r="D52" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E52" t="s">
         <v>11</v>
       </c>
       <c r="G52" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H52" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>52</v>
       </c>
       <c r="B53" t="s">
+        <v>109</v>
+      </c>
+      <c r="C53" t="s">
+        <v>97</v>
+      </c>
+      <c r="D53" t="s">
         <v>110</v>
       </c>
-      <c r="C53" t="s">
-        <v>98</v>
-      </c>
-      <c r="D53" t="s">
+      <c r="E53" t="s">
+        <v>11</v>
+      </c>
+      <c r="G53" t="s">
         <v>111</v>
       </c>
-      <c r="E53" t="s">
-        <v>11</v>
-      </c>
-      <c r="G53" t="s">
-        <v>112</v>
-      </c>
       <c r="H53" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C54" t="s">
+        <v>112</v>
+      </c>
+      <c r="D54" t="s">
         <v>113</v>
       </c>
-      <c r="D54" t="s">
-        <v>114</v>
-      </c>
       <c r="E54" t="s">
         <v>11</v>
       </c>
       <c r="G54" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H54" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C55" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D55" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E55" t="s">
         <v>11</v>
       </c>
       <c r="G55" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H55" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C56" t="s">
+        <v>115</v>
+      </c>
+      <c r="D56" t="s">
         <v>116</v>
       </c>
-      <c r="D56" t="s">
-        <v>117</v>
-      </c>
       <c r="E56" t="s">
         <v>11</v>
       </c>
       <c r="G56" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H56" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C57" t="s">
         <v>9</v>
       </c>
       <c r="D57" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E57" t="s">
         <v>11</v>
       </c>
       <c r="G57" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H57" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C58" t="s">
         <v>9</v>
       </c>
       <c r="D58" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E58" t="s">
         <v>11</v>
       </c>
       <c r="G58" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H58" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>58</v>
       </c>
       <c r="B59" t="s">
+        <v>118</v>
+      </c>
+      <c r="C59" t="s">
+        <v>120</v>
+      </c>
+      <c r="D59" t="s">
+        <v>19</v>
+      </c>
+      <c r="E59" t="s">
+        <v>11</v>
+      </c>
+      <c r="G59" t="s">
         <v>119</v>
       </c>
-      <c r="C59" t="s">
-        <v>121</v>
-      </c>
-      <c r="D59" t="s">
-        <v>20</v>
-      </c>
-      <c r="E59" t="s">
-        <v>11</v>
-      </c>
-      <c r="G59" t="s">
-        <v>120</v>
-      </c>
       <c r="H59" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>59</v>
       </c>
       <c r="B60" t="s">
+        <v>121</v>
+      </c>
+      <c r="C60" t="s">
+        <v>16</v>
+      </c>
+      <c r="D60" t="s">
         <v>122</v>
       </c>
-      <c r="C60" t="s">
-        <v>17</v>
-      </c>
-      <c r="D60" t="s">
-        <v>123</v>
-      </c>
       <c r="E60" t="s">
         <v>11</v>
       </c>
       <c r="G60" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H60" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>60</v>
       </c>
       <c r="B61" t="s">
+        <v>123</v>
+      </c>
+      <c r="C61" t="s">
         <v>124</v>
       </c>
-      <c r="C61" t="s">
+      <c r="D61" t="s">
         <v>125</v>
       </c>
-      <c r="D61" t="s">
+      <c r="E61" t="s">
+        <v>11</v>
+      </c>
+      <c r="G61" t="s">
         <v>126</v>
       </c>
-      <c r="E61" t="s">
-        <v>11</v>
-      </c>
-      <c r="G61" t="s">
-        <v>127</v>
-      </c>
       <c r="H61" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C62" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D62" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E62" t="s">
         <v>11</v>
       </c>
       <c r="G62" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H62" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C63" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D63" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E63" t="s">
         <v>11</v>
       </c>
       <c r="G63" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H63" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C64" t="s">
+        <v>129</v>
+      </c>
+      <c r="D64" t="s">
         <v>130</v>
       </c>
-      <c r="D64" t="s">
-        <v>131</v>
-      </c>
       <c r="E64" t="s">
         <v>11</v>
       </c>
       <c r="G64" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H64" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C65" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D65" t="s">
+        <v>131</v>
+      </c>
+      <c r="E65" t="s">
         <v>132</v>
       </c>
-      <c r="E65" t="s">
-        <v>133</v>
-      </c>
       <c r="G65" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H65" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C66" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D66" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E66" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G66" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H66" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C67" t="s">
+        <v>134</v>
+      </c>
+      <c r="D67" t="s">
         <v>135</v>
       </c>
-      <c r="D67" t="s">
-        <v>136</v>
-      </c>
       <c r="E67" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G67" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H67" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C68" t="s">
         <v>9</v>
       </c>
       <c r="D68" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E68" t="s">
         <v>11</v>
       </c>
       <c r="G68" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H68" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C69" t="s">
         <v>9</v>
       </c>
       <c r="D69" t="s">
+        <v>137</v>
+      </c>
+      <c r="E69" t="s">
+        <v>11</v>
+      </c>
+      <c r="G69" t="s">
         <v>138</v>
       </c>
-      <c r="E69" t="s">
-        <v>11</v>
-      </c>
-      <c r="G69" t="s">
-        <v>139</v>
-      </c>
       <c r="H69" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C70" t="s">
+        <v>139</v>
+      </c>
+      <c r="D70" t="s">
         <v>140</v>
       </c>
-      <c r="D70" t="s">
-        <v>141</v>
-      </c>
       <c r="E70" t="s">
         <v>11</v>
       </c>
       <c r="G70" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H70" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>70</v>
       </c>
       <c r="B71" t="s">
+        <v>141</v>
+      </c>
+      <c r="C71" t="s">
         <v>142</v>
       </c>
-      <c r="C71" t="s">
+      <c r="D71" t="s">
         <v>143</v>
       </c>
-      <c r="D71" t="s">
-        <v>144</v>
-      </c>
       <c r="E71" t="s">
         <v>11</v>
       </c>
       <c r="G71" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H71" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C72" t="s">
+        <v>144</v>
+      </c>
+      <c r="D72" t="s">
         <v>145</v>
       </c>
-      <c r="D72" t="s">
-        <v>146</v>
-      </c>
       <c r="E72" t="s">
         <v>11</v>
       </c>
       <c r="G72" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H72" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C73" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D73" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E73" t="s">
         <v>11</v>
       </c>
       <c r="G73" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H73" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>73</v>
       </c>
       <c r="B74" t="s">
+        <v>146</v>
+      </c>
+      <c r="C74" t="s">
+        <v>32</v>
+      </c>
+      <c r="D74" t="s">
         <v>147</v>
       </c>
-      <c r="C74" t="s">
-        <v>33</v>
-      </c>
-      <c r="D74" t="s">
-        <v>148</v>
-      </c>
       <c r="E74" t="s">
         <v>11</v>
       </c>
       <c r="G74" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H74" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C75" t="s">
+        <v>148</v>
+      </c>
+      <c r="D75" t="s">
         <v>149</v>
       </c>
-      <c r="D75" t="s">
+      <c r="E75" t="s">
+        <v>11</v>
+      </c>
+      <c r="G75" t="s">
         <v>150</v>
       </c>
-      <c r="E75" t="s">
-        <v>11</v>
-      </c>
-      <c r="G75" t="s">
-        <v>151</v>
-      </c>
       <c r="H75" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>75</v>
       </c>
       <c r="B76" t="s">
+        <v>151</v>
+      </c>
+      <c r="C76" t="s">
         <v>152</v>
       </c>
-      <c r="C76" t="s">
-        <v>153</v>
-      </c>
       <c r="D76" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E76" t="s">
         <v>11</v>
       </c>
       <c r="G76" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H76" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C77" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D77" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E77" t="s">
         <v>11</v>
       </c>
       <c r="G77" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H77" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C78" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D78" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E78" t="s">
         <v>11</v>
       </c>
       <c r="G78" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H78" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C79" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D79" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E79" t="s">
         <v>11</v>
       </c>
       <c r="G79" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H79" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C80" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D80" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E80" t="s">
         <v>11</v>
       </c>
       <c r="G80" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H80" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C81" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D81" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E81" t="s">
         <v>11</v>
       </c>
       <c r="G81" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H81" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C82" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D82" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E82" t="s">
         <v>11</v>
       </c>
       <c r="G82" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H82" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C83" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D83" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E83" t="s">
         <v>11</v>
       </c>
       <c r="G83" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H83" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C84" t="s">
+        <v>158</v>
+      </c>
+      <c r="D84" t="s">
         <v>159</v>
       </c>
-      <c r="D84" t="s">
-        <v>160</v>
-      </c>
       <c r="E84" t="s">
         <v>11</v>
       </c>
       <c r="G84" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H84" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C85" t="s">
+        <v>160</v>
+      </c>
+      <c r="D85" t="s">
         <v>161</v>
       </c>
-      <c r="D85" t="s">
-        <v>162</v>
-      </c>
       <c r="E85" t="s">
         <v>11</v>
       </c>
       <c r="G85" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H85" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C86" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D86" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E86" t="s">
+        <v>74</v>
+      </c>
+      <c r="G86" t="s">
         <v>75</v>
       </c>
-      <c r="G86" t="s">
-        <v>76</v>
-      </c>
       <c r="H86" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>86</v>
       </c>
       <c r="B87" t="s">
+        <v>162</v>
+      </c>
+      <c r="C87" t="s">
         <v>163</v>
       </c>
-      <c r="C87" t="s">
+      <c r="D87" t="s">
         <v>164</v>
       </c>
-      <c r="D87" t="s">
+      <c r="E87" t="s">
+        <v>11</v>
+      </c>
+      <c r="G87" t="s">
         <v>165</v>
       </c>
-      <c r="E87" t="s">
-        <v>11</v>
-      </c>
-      <c r="G87" t="s">
-        <v>166</v>
-      </c>
       <c r="H87" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C88" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D88" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E88" t="s">
         <v>11</v>
       </c>
       <c r="G88" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H88" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C89" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D89" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E89" t="s">
         <v>11</v>
       </c>
       <c r="G89" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H89" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C90" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D90" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E90" t="s">
         <v>11</v>
       </c>
       <c r="G90" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H90" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C91" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D91" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E91" t="s">
         <v>11</v>
       </c>
       <c r="G91" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H91" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C92" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D92" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E92" t="s">
         <v>11</v>
       </c>
       <c r="G92" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H92" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C93" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D93" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E93" t="s">
         <v>11</v>
       </c>
       <c r="G93" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H93" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C94" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D94" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E94" t="s">
         <v>11</v>
       </c>
       <c r="G94" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H94" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C95" t="s">
+        <v>173</v>
+      </c>
+      <c r="D95" t="s">
         <v>174</v>
       </c>
-      <c r="D95" t="s">
-        <v>175</v>
-      </c>
       <c r="E95" t="s">
         <v>11</v>
       </c>
       <c r="G95" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H95" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C96" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D96" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E96" t="s">
         <v>11</v>
       </c>
       <c r="G96" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H96" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C97" t="s">
+        <v>176</v>
+      </c>
+      <c r="D97" t="s">
         <v>177</v>
       </c>
-      <c r="D97" t="s">
-        <v>178</v>
-      </c>
       <c r="E97" t="s">
         <v>11</v>
       </c>
       <c r="G97" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H97" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C98" t="s">
+        <v>178</v>
+      </c>
+      <c r="D98" t="s">
         <v>179</v>
       </c>
-      <c r="D98" t="s">
-        <v>180</v>
-      </c>
       <c r="E98" t="s">
         <v>11</v>
       </c>
       <c r="G98" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H98" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C99" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D99" t="s">
+        <v>22</v>
+      </c>
+      <c r="E99" t="s">
+        <v>11</v>
+      </c>
+      <c r="G99" t="s">
         <v>23</v>
       </c>
-      <c r="E99" t="s">
-        <v>11</v>
-      </c>
-      <c r="G99" t="s">
-        <v>24</v>
-      </c>
       <c r="H99" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>99</v>
       </c>
       <c r="B100" t="s">
+        <v>180</v>
+      </c>
+      <c r="C100" t="s">
         <v>181</v>
       </c>
-      <c r="C100" t="s">
+      <c r="D100" t="s">
         <v>182</v>
       </c>
-      <c r="D100" t="s">
-        <v>183</v>
-      </c>
       <c r="E100" t="s">
         <v>11</v>
       </c>
       <c r="G100" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H100" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C101" t="s">
+        <v>183</v>
+      </c>
+      <c r="D101" t="s">
         <v>184</v>
       </c>
-      <c r="D101" t="s">
-        <v>185</v>
-      </c>
       <c r="E101" t="s">
         <v>11</v>
       </c>
       <c r="G101" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H101" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>101</v>
       </c>
       <c r="B102" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C102" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D102" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E102" t="s">
         <v>11</v>
       </c>
       <c r="G102" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H102" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>102</v>
       </c>
       <c r="B103" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C103" t="s">
+        <v>186</v>
+      </c>
+      <c r="D103" t="s">
         <v>187</v>
       </c>
-      <c r="D103" t="s">
+      <c r="E103" t="s">
+        <v>11</v>
+      </c>
+      <c r="G103" t="s">
         <v>188</v>
       </c>
-      <c r="E103" t="s">
-        <v>11</v>
-      </c>
-      <c r="G103" t="s">
-        <v>189</v>
-      </c>
       <c r="H103" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>103</v>
       </c>
       <c r="B104" t="s">
+        <v>189</v>
+      </c>
+      <c r="C104" t="s">
         <v>190</v>
       </c>
-      <c r="C104" t="s">
+      <c r="D104" t="s">
         <v>191</v>
       </c>
-      <c r="D104" t="s">
-        <v>192</v>
-      </c>
       <c r="E104" t="s">
         <v>11</v>
       </c>
       <c r="G104" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H104" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>104</v>
       </c>
       <c r="B105" t="s">
+        <v>192</v>
+      </c>
+      <c r="C105" t="s">
+        <v>86</v>
+      </c>
+      <c r="D105" t="s">
         <v>193</v>
       </c>
-      <c r="C105" t="s">
-        <v>87</v>
-      </c>
-      <c r="D105" t="s">
-        <v>194</v>
-      </c>
       <c r="E105" t="s">
         <v>11</v>
       </c>
       <c r="G105" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H105" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>105</v>
       </c>
       <c r="B106" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C106" t="s">
+        <v>194</v>
+      </c>
+      <c r="D106" t="s">
         <v>195</v>
       </c>
-      <c r="D106" t="s">
-        <v>196</v>
-      </c>
       <c r="E106" t="s">
         <v>11</v>
       </c>
       <c r="G106" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H106" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>106</v>
       </c>
       <c r="B107" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C107" t="s">
+        <v>196</v>
+      </c>
+      <c r="D107" t="s">
         <v>197</v>
       </c>
-      <c r="D107" t="s">
-        <v>198</v>
-      </c>
       <c r="E107" t="s">
         <v>11</v>
       </c>
       <c r="G107" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H107" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>107</v>
       </c>
       <c r="B108" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C108" t="s">
+        <v>198</v>
+      </c>
+      <c r="D108" t="s">
         <v>199</v>
       </c>
-      <c r="D108" t="s">
-        <v>200</v>
-      </c>
       <c r="E108" t="s">
         <v>11</v>
       </c>
       <c r="G108" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H108" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>108</v>
       </c>
       <c r="B109" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C109" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D109" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E109" t="s">
         <v>11</v>
       </c>
       <c r="G109" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H109" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>109</v>
       </c>
       <c r="B110" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C110" t="s">
+        <v>201</v>
+      </c>
+      <c r="D110" t="s">
         <v>202</v>
       </c>
-      <c r="D110" t="s">
-        <v>203</v>
-      </c>
       <c r="E110" t="s">
         <v>11</v>
       </c>
       <c r="G110" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H110" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>110</v>
       </c>
       <c r="B111" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C111" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D111" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E111" t="s">
         <v>11</v>
       </c>
       <c r="G111" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H111" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>111</v>
       </c>
       <c r="B112" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C112" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D112" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E112" t="s">
+        <v>74</v>
+      </c>
+      <c r="G112" t="s">
         <v>75</v>
       </c>
-      <c r="G112" t="s">
-        <v>76</v>
-      </c>
       <c r="H112" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>112</v>
       </c>
       <c r="B113" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C113" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D113" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E113" t="s">
         <v>11</v>
       </c>
       <c r="G113" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H113" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>113</v>
       </c>
       <c r="B114" t="s">
+        <v>205</v>
+      </c>
+      <c r="C114" t="s">
+        <v>97</v>
+      </c>
+      <c r="D114" t="s">
+        <v>98</v>
+      </c>
+      <c r="E114" t="s">
+        <v>11</v>
+      </c>
+      <c r="G114" t="s">
         <v>206</v>
       </c>
-      <c r="C114" t="s">
-        <v>98</v>
-      </c>
-      <c r="D114" t="s">
-        <v>99</v>
-      </c>
-      <c r="E114" t="s">
-        <v>11</v>
-      </c>
-      <c r="G114" t="s">
-        <v>207</v>
-      </c>
       <c r="H114" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>114</v>
       </c>
       <c r="B115" t="s">
+        <v>207</v>
+      </c>
+      <c r="C115" t="s">
         <v>208</v>
       </c>
-      <c r="C115" t="s">
+      <c r="D115" t="s">
         <v>209</v>
       </c>
-      <c r="D115" t="s">
+      <c r="E115" t="s">
+        <v>11</v>
+      </c>
+      <c r="G115" t="s">
         <v>210</v>
       </c>
-      <c r="E115" t="s">
-        <v>11</v>
-      </c>
-      <c r="G115" t="s">
-        <v>211</v>
-      </c>
       <c r="H115" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>115</v>
       </c>
       <c r="B116" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C116" t="s">
+        <v>211</v>
+      </c>
+      <c r="D116" t="s">
         <v>212</v>
       </c>
-      <c r="D116" t="s">
-        <v>213</v>
-      </c>
       <c r="E116" t="s">
         <v>11</v>
       </c>
       <c r="G116" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H116" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>116</v>
       </c>
       <c r="B117" t="s">
+        <v>213</v>
+      </c>
+      <c r="C117" t="s">
         <v>214</v>
       </c>
-      <c r="C117" t="s">
-        <v>215</v>
-      </c>
       <c r="D117" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E117" t="s">
         <v>11</v>
       </c>
       <c r="G117" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H117" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>117</v>
       </c>
       <c r="B118" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C118" t="s">
+        <v>215</v>
+      </c>
+      <c r="D118" t="s">
         <v>216</v>
       </c>
-      <c r="D118" t="s">
-        <v>217</v>
-      </c>
       <c r="E118" t="s">
         <v>11</v>
       </c>
       <c r="G118" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H118" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>118</v>
       </c>
       <c r="B119" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C119" t="s">
         <v>9</v>
       </c>
       <c r="D119" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E119" t="s">
         <v>11</v>
       </c>
       <c r="G119" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H119" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>119</v>
       </c>
       <c r="B120" t="s">
+        <v>217</v>
+      </c>
+      <c r="C120" t="s">
         <v>218</v>
       </c>
-      <c r="C120" t="s">
+      <c r="D120" t="s">
         <v>219</v>
       </c>
-      <c r="D120" t="s">
+      <c r="E120" t="s">
+        <v>11</v>
+      </c>
+      <c r="G120" t="s">
         <v>220</v>
       </c>
-      <c r="E120" t="s">
-        <v>11</v>
-      </c>
-      <c r="G120" t="s">
-        <v>221</v>
-      </c>
       <c r="H120" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>120</v>
       </c>
       <c r="B121" t="s">
+        <v>221</v>
+      </c>
+      <c r="C121" t="s">
+        <v>16</v>
+      </c>
+      <c r="D121" t="s">
+        <v>114</v>
+      </c>
+      <c r="E121" t="s">
+        <v>11</v>
+      </c>
+      <c r="G121" t="s">
         <v>222</v>
       </c>
-      <c r="C121" t="s">
-        <v>17</v>
-      </c>
-      <c r="D121" t="s">
-        <v>115</v>
-      </c>
-      <c r="E121" t="s">
-        <v>11</v>
-      </c>
-      <c r="G121" t="s">
-        <v>223</v>
-      </c>
       <c r="H121" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>121</v>
       </c>
       <c r="B122" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C122" t="s">
         <v>9</v>
       </c>
       <c r="D122" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E122" t="s">
         <v>11</v>
       </c>
       <c r="G122" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H122" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>122</v>
       </c>
       <c r="B123" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C123" t="s">
         <v>9</v>
       </c>
       <c r="D123" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E123" t="s">
         <v>11</v>
       </c>
       <c r="G123" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H123" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>123</v>
       </c>
       <c r="B124" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C124" t="s">
         <v>9</v>
       </c>
       <c r="D124" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E124" t="s">
+        <v>74</v>
+      </c>
+      <c r="G124" t="s">
         <v>75</v>
       </c>
-      <c r="G124" t="s">
-        <v>76</v>
-      </c>
       <c r="H124" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>124</v>
       </c>
       <c r="B125" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C125" t="s">
+        <v>224</v>
+      </c>
+      <c r="D125" t="s">
+        <v>98</v>
+      </c>
+      <c r="E125" t="s">
+        <v>11</v>
+      </c>
+      <c r="G125" t="s">
         <v>225</v>
       </c>
-      <c r="D125" t="s">
-        <v>99</v>
-      </c>
-      <c r="E125" t="s">
-        <v>11</v>
-      </c>
-      <c r="G125" t="s">
-        <v>226</v>
-      </c>
       <c r="H125" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>125</v>
       </c>
       <c r="B126" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C126" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D126" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E126" t="s">
         <v>11</v>
       </c>
       <c r="G126" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H126" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>126</v>
       </c>
       <c r="B127" t="s">
+        <v>226</v>
+      </c>
+      <c r="C127" t="s">
         <v>227</v>
       </c>
-      <c r="C127" t="s">
+      <c r="D127" t="s">
         <v>228</v>
       </c>
-      <c r="D127" t="s">
+      <c r="E127" t="s">
+        <v>11</v>
+      </c>
+      <c r="G127" t="s">
         <v>229</v>
       </c>
-      <c r="E127" t="s">
-        <v>11</v>
-      </c>
-      <c r="G127" t="s">
-        <v>230</v>
-      </c>
       <c r="H127" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>127</v>
       </c>
       <c r="B128" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C128" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D128" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E128" t="s">
         <v>11</v>
       </c>
       <c r="G128" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H128" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>128</v>
       </c>
       <c r="B129" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C129" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D129" t="s">
+        <v>231</v>
+      </c>
+      <c r="E129" t="s">
+        <v>11</v>
+      </c>
+      <c r="G129" t="s">
         <v>232</v>
       </c>
-      <c r="E129" t="s">
-        <v>11</v>
-      </c>
-      <c r="G129" t="s">
-        <v>233</v>
-      </c>
       <c r="H129" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>129</v>
       </c>
       <c r="B130" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C130" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D130" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E130" t="s">
         <v>11</v>
       </c>
       <c r="G130" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H130" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>130</v>
       </c>
       <c r="B131" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C131" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D131" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E131" t="s">
         <v>11</v>
       </c>
       <c r="G131" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H131" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>131</v>
       </c>
       <c r="B132" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C132" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D132" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E132" t="s">
         <v>11</v>
       </c>
       <c r="G132" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H132" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>132</v>
       </c>
       <c r="B133" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C133" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D133" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E133" t="s">
         <v>11</v>
       </c>
       <c r="G133" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H133" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>133</v>
       </c>
       <c r="B134" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C134" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D134" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E134" t="s">
         <v>11</v>
       </c>
       <c r="G134" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H134" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>134</v>
       </c>
       <c r="B135" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C135" t="s">
+        <v>237</v>
+      </c>
+      <c r="D135" t="s">
         <v>238</v>
       </c>
-      <c r="D135" t="s">
-        <v>239</v>
-      </c>
       <c r="E135" t="s">
         <v>11</v>
       </c>
       <c r="G135" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H135" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>135</v>
       </c>
       <c r="B136" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C136" t="s">
         <v>9</v>
       </c>
       <c r="D136" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E136" t="s">
         <v>11</v>
       </c>
       <c r="G136" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H136" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>136</v>
       </c>
       <c r="B137" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C137" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D137" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E137" t="s">
         <v>11</v>
       </c>
       <c r="G137" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H137" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>137</v>
       </c>
       <c r="B138" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C138" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D138" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E138" t="s">
         <v>11</v>
       </c>
       <c r="G138" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H138" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>138</v>
       </c>
       <c r="B139" t="s">
+        <v>241</v>
+      </c>
+      <c r="C139" t="s">
         <v>242</v>
       </c>
-      <c r="C139" t="s">
-        <v>243</v>
-      </c>
       <c r="D139" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E139" t="s">
         <v>11</v>
       </c>
       <c r="G139" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H139" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>139</v>
       </c>
       <c r="B140" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C140" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D140" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E140" t="s">
         <v>11</v>
       </c>
       <c r="G140" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H140" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>140</v>
       </c>
       <c r="B141" t="s">
+        <v>243</v>
+      </c>
+      <c r="C141" t="s">
         <v>244</v>
       </c>
-      <c r="C141" t="s">
-        <v>245</v>
-      </c>
       <c r="D141" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E141" t="s">
         <v>11</v>
       </c>
       <c r="G141" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H141" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>141</v>
       </c>
       <c r="B142" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C142" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D142" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E142" t="s">
         <v>11</v>
       </c>
       <c r="G142" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H142" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>142</v>
       </c>
       <c r="B143" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C143" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D143" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E143" t="s">
         <v>11</v>
       </c>
       <c r="G143" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H143" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>143</v>
       </c>
       <c r="B144" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C144" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D144" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E144" t="s">
         <v>11</v>
       </c>
       <c r="G144" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H144" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>144</v>
       </c>
       <c r="B145" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C145" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D145" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E145" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G145" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H145" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>145</v>
       </c>
       <c r="B146" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C146" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D146" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E146" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G146" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H146" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>146</v>
       </c>
       <c r="B147" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C147" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D147" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E147" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G147" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H147" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>147</v>
       </c>
       <c r="B148" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C148" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D148" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E148" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G148" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H148" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>148</v>
       </c>
       <c r="B149" t="s">
+        <v>250</v>
+      </c>
+      <c r="C149" t="s">
         <v>251</v>
       </c>
-      <c r="C149" t="s">
-        <v>252</v>
-      </c>
       <c r="D149" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E149" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G149" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H149" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>149</v>
       </c>
       <c r="B150" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C150" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D150" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E150" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G150" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H150" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>150</v>
       </c>
       <c r="B151" t="s">
+        <v>252</v>
+      </c>
+      <c r="C151" t="s">
+        <v>124</v>
+      </c>
+      <c r="D151" t="s">
         <v>253</v>
       </c>
-      <c r="C151" t="s">
-        <v>125</v>
-      </c>
-      <c r="D151" t="s">
-        <v>254</v>
-      </c>
       <c r="E151" t="s">
+        <v>74</v>
+      </c>
+      <c r="G151" t="s">
         <v>75</v>
       </c>
-      <c r="G151" t="s">
-        <v>76</v>
-      </c>
       <c r="H151" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>151</v>
       </c>
       <c r="B152" t="s">
+        <v>254</v>
+      </c>
+      <c r="C152" t="s">
         <v>255</v>
       </c>
-      <c r="C152" t="s">
+      <c r="D152" t="s">
         <v>256</v>
       </c>
-      <c r="D152" t="s">
-        <v>257</v>
-      </c>
       <c r="E152" t="s">
+        <v>74</v>
+      </c>
+      <c r="G152" t="s">
         <v>75</v>
       </c>
-      <c r="G152" t="s">
-        <v>76</v>
-      </c>
       <c r="H152" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>152</v>
       </c>
       <c r="B153" t="s">
+        <v>257</v>
+      </c>
+      <c r="D153" t="s">
         <v>258</v>
       </c>
-      <c r="D153" t="s">
+      <c r="H153" t="s">
         <v>259</v>
       </c>
-      <c r="H153" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="154" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>153</v>
       </c>
       <c r="B154" t="s">
+        <v>257</v>
+      </c>
+      <c r="D154" t="s">
         <v>258</v>
       </c>
-      <c r="D154" t="s">
+      <c r="H154" t="s">
         <v>259</v>
       </c>
-      <c r="H154" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="155" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>154</v>
       </c>
       <c r="B155" t="s">
+        <v>257</v>
+      </c>
+      <c r="D155" t="s">
         <v>258</v>
       </c>
-      <c r="D155" t="s">
+      <c r="H155" t="s">
         <v>259</v>
       </c>
-      <c r="H155" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="156" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>155</v>
       </c>
       <c r="B156" t="s">
+        <v>257</v>
+      </c>
+      <c r="D156" t="s">
         <v>258</v>
       </c>
-      <c r="D156" t="s">
+      <c r="H156" t="s">
         <v>259</v>
       </c>
-      <c r="H156" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="157" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>156</v>
       </c>
       <c r="B157" t="s">
+        <v>257</v>
+      </c>
+      <c r="D157" t="s">
         <v>258</v>
       </c>
-      <c r="D157" t="s">
+      <c r="H157" t="s">
         <v>259</v>
       </c>
-      <c r="H157" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="158" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158">
         <v>157</v>
       </c>
       <c r="B158" t="s">
+        <v>257</v>
+      </c>
+      <c r="D158" t="s">
         <v>258</v>
       </c>
-      <c r="D158" t="s">
+      <c r="H158" t="s">
         <v>259</v>
       </c>
-      <c r="H158" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="159" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>158</v>
       </c>
       <c r="B159" t="s">
+        <v>257</v>
+      </c>
+      <c r="D159" t="s">
         <v>258</v>
       </c>
-      <c r="D159" t="s">
+      <c r="H159" t="s">
         <v>259</v>
       </c>
-      <c r="H159" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="160" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>159</v>
       </c>
       <c r="B160" t="s">
+        <v>257</v>
+      </c>
+      <c r="D160" t="s">
         <v>258</v>
       </c>
-      <c r="D160" t="s">
+      <c r="H160" t="s">
         <v>259</v>
       </c>
-      <c r="H160" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="161" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="161" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>160</v>
       </c>
       <c r="B161" t="s">
+        <v>257</v>
+      </c>
+      <c r="D161" t="s">
         <v>258</v>
       </c>
-      <c r="D161" t="s">
+      <c r="H161" t="s">
         <v>259</v>
       </c>
-      <c r="H161" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="162" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="162" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>161</v>
       </c>
       <c r="B162" t="s">
+        <v>257</v>
+      </c>
+      <c r="D162" t="s">
         <v>258</v>
       </c>
-      <c r="D162" t="s">
+      <c r="H162" t="s">
         <v>259</v>
       </c>
-      <c r="H162" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="163" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="163" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>162</v>
       </c>
       <c r="B163" t="s">
+        <v>257</v>
+      </c>
+      <c r="D163" t="s">
         <v>258</v>
       </c>
-      <c r="D163" t="s">
+      <c r="H163" t="s">
         <v>259</v>
       </c>
-      <c r="H163" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="164" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="164" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>163</v>
       </c>
       <c r="B164" t="s">
+        <v>257</v>
+      </c>
+      <c r="D164" t="s">
         <v>258</v>
       </c>
-      <c r="D164" t="s">
+      <c r="H164" t="s">
         <v>259</v>
       </c>
-      <c r="H164" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="165" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="165" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>164</v>
       </c>
       <c r="B165" t="s">
+        <v>257</v>
+      </c>
+      <c r="D165" t="s">
         <v>258</v>
       </c>
-      <c r="D165" t="s">
+      <c r="H165" t="s">
         <v>259</v>
       </c>
-      <c r="H165" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="166" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="166" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>165</v>
       </c>
       <c r="B166" t="s">
+        <v>257</v>
+      </c>
+      <c r="D166" t="s">
         <v>258</v>
       </c>
-      <c r="D166" t="s">
+      <c r="H166" t="s">
         <v>259</v>
       </c>
-      <c r="H166" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="167" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="167" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>166</v>
       </c>
       <c r="B167" t="s">
+        <v>257</v>
+      </c>
+      <c r="D167" t="s">
         <v>258</v>
       </c>
-      <c r="D167" t="s">
+      <c r="H167" t="s">
         <v>259</v>
       </c>
-      <c r="H167" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="168" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>167</v>
       </c>
       <c r="B168" t="s">
+        <v>257</v>
+      </c>
+      <c r="D168" t="s">
         <v>258</v>
       </c>
-      <c r="D168" t="s">
+      <c r="H168" t="s">
         <v>259</v>
       </c>
-      <c r="H168" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="169" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="169" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>168</v>
       </c>
       <c r="B169" t="s">
+        <v>257</v>
+      </c>
+      <c r="D169" t="s">
         <v>258</v>
       </c>
-      <c r="D169" t="s">
+      <c r="H169" t="s">
         <v>259</v>
       </c>
-      <c r="H169" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="170" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="170" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>169</v>
       </c>
       <c r="B170" t="s">
+        <v>257</v>
+      </c>
+      <c r="D170" t="s">
         <v>258</v>
       </c>
-      <c r="D170" t="s">
+      <c r="H170" t="s">
         <v>259</v>
       </c>
-      <c r="H170" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="171" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="171" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>170</v>
       </c>
       <c r="B171" t="s">
+        <v>257</v>
+      </c>
+      <c r="D171" t="s">
         <v>258</v>
       </c>
-      <c r="D171" t="s">
+      <c r="H171" t="s">
         <v>259</v>
       </c>
-      <c r="H171" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="172" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="172" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>171</v>
       </c>
       <c r="B172" t="s">
+        <v>257</v>
+      </c>
+      <c r="D172" t="s">
         <v>258</v>
       </c>
-      <c r="D172" t="s">
+      <c r="H172" t="s">
         <v>259</v>
       </c>
-      <c r="H172" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="173" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="173" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>172</v>
       </c>
       <c r="B173" t="s">
+        <v>257</v>
+      </c>
+      <c r="D173" t="s">
         <v>258</v>
       </c>
-      <c r="D173" t="s">
+      <c r="H173" t="s">
         <v>259</v>
       </c>
-      <c r="H173" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="174" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="174" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>173</v>
       </c>
       <c r="B174" t="s">
+        <v>257</v>
+      </c>
+      <c r="D174" t="s">
         <v>258</v>
       </c>
-      <c r="D174" t="s">
+      <c r="H174" t="s">
         <v>259</v>
       </c>
-      <c r="H174" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="175" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="175" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>174</v>
       </c>
       <c r="B175" t="s">
+        <v>257</v>
+      </c>
+      <c r="D175" t="s">
         <v>258</v>
       </c>
-      <c r="D175" t="s">
+      <c r="H175" t="s">
         <v>259</v>
       </c>
-      <c r="H175" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="176" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="176" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176">
         <v>175</v>
       </c>
       <c r="B176" t="s">
+        <v>257</v>
+      </c>
+      <c r="D176" t="s">
         <v>258</v>
       </c>
-      <c r="D176" t="s">
+      <c r="H176" t="s">
         <v>259</v>
       </c>
-      <c r="H176" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="177" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="177" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>176</v>
       </c>
       <c r="B177" t="s">
+        <v>257</v>
+      </c>
+      <c r="D177" t="s">
         <v>258</v>
       </c>
-      <c r="D177" t="s">
+      <c r="H177" t="s">
         <v>259</v>
       </c>
-      <c r="H177" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="178" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="178" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178">
         <v>177</v>
       </c>
       <c r="B178" t="s">
+        <v>257</v>
+      </c>
+      <c r="D178" t="s">
         <v>258</v>
       </c>
-      <c r="D178" t="s">
+      <c r="H178" t="s">
         <v>259</v>
       </c>
-      <c r="H178" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="179" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="179" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>178</v>
       </c>
       <c r="B179" t="s">
+        <v>257</v>
+      </c>
+      <c r="D179" t="s">
         <v>258</v>
       </c>
-      <c r="D179" t="s">
+      <c r="H179" t="s">
         <v>259</v>
       </c>
-      <c r="H179" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="180" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="180" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180">
         <v>179</v>
       </c>
       <c r="B180" t="s">
+        <v>257</v>
+      </c>
+      <c r="D180" t="s">
         <v>258</v>
       </c>
-      <c r="D180" t="s">
+      <c r="H180" t="s">
         <v>259</v>
       </c>
-      <c r="H180" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="181" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="181" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>180</v>
       </c>
       <c r="B181" t="s">
+        <v>257</v>
+      </c>
+      <c r="D181" t="s">
         <v>258</v>
       </c>
-      <c r="D181" t="s">
+      <c r="H181" t="s">
         <v>259</v>
       </c>
-      <c r="H181" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="182" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="182" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182">
         <v>181</v>
       </c>
       <c r="B182" t="s">
+        <v>257</v>
+      </c>
+      <c r="D182" t="s">
         <v>258</v>
       </c>
-      <c r="D182" t="s">
+      <c r="H182" t="s">
         <v>259</v>
       </c>
-      <c r="H182" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="183" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="183" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183">
         <v>182</v>
       </c>
       <c r="B183" t="s">
+        <v>257</v>
+      </c>
+      <c r="D183" t="s">
         <v>258</v>
       </c>
-      <c r="D183" t="s">
+      <c r="H183" t="s">
         <v>259</v>
       </c>
-      <c r="H183" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="184" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="184" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184">
         <v>183</v>
       </c>
       <c r="B184" t="s">
+        <v>257</v>
+      </c>
+      <c r="D184" t="s">
         <v>258</v>
       </c>
-      <c r="D184" t="s">
+      <c r="H184" t="s">
         <v>259</v>
       </c>
-      <c r="H184" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="185" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="185" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185">
         <v>184</v>
       </c>
       <c r="B185" t="s">
+        <v>257</v>
+      </c>
+      <c r="D185" t="s">
         <v>258</v>
       </c>
-      <c r="D185" t="s">
+      <c r="H185" t="s">
         <v>259</v>
       </c>
-      <c r="H185" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="186" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="186" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186">
         <v>185</v>
       </c>
       <c r="B186" t="s">
+        <v>257</v>
+      </c>
+      <c r="D186" t="s">
         <v>258</v>
       </c>
-      <c r="D186" t="s">
+      <c r="H186" t="s">
         <v>259</v>
       </c>
-      <c r="H186" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="187" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="187" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>186</v>
       </c>
       <c r="B187" t="s">
+        <v>257</v>
+      </c>
+      <c r="D187" t="s">
         <v>258</v>
       </c>
-      <c r="D187" t="s">
+      <c r="H187" t="s">
         <v>259</v>
       </c>
-      <c r="H187" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="188" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="188" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188">
         <v>187</v>
       </c>
       <c r="B188" t="s">
+        <v>257</v>
+      </c>
+      <c r="D188" t="s">
         <v>258</v>
       </c>
-      <c r="D188" t="s">
+      <c r="H188" t="s">
         <v>259</v>
       </c>
-      <c r="H188" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="189" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="189" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189">
         <v>188</v>
       </c>
       <c r="B189" t="s">
+        <v>257</v>
+      </c>
+      <c r="D189" t="s">
         <v>258</v>
       </c>
-      <c r="D189" t="s">
+      <c r="H189" t="s">
         <v>259</v>
       </c>
-      <c r="H189" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="190" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="190" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190">
         <v>189</v>
       </c>
       <c r="B190" t="s">
+        <v>257</v>
+      </c>
+      <c r="D190" t="s">
         <v>258</v>
       </c>
-      <c r="D190" t="s">
+      <c r="H190" t="s">
         <v>259</v>
-      </c>
-      <c r="H190" t="s">
-        <v>260</v>
-      </c>
-    </row>
-  </sheetData>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="2" width="15" customWidth="1"/>
-    <col min="3" max="3" width="20" customWidth="1"/>
-    <col min="4" max="5" width="15" customWidth="1"/>
-    <col min="6" max="6" width="30" customWidth="1"/>
-    <col min="7" max="8" width="15" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>261</v>
-      </c>
-      <c r="B1" t="s">
-        <v>262</v>
-      </c>
-      <c r="C1" t="s">
-        <v>263</v>
-      </c>
-      <c r="D1" t="s">
-        <v>264</v>
-      </c>
-      <c r="E1" t="s">
-        <v>265</v>
-      </c>
-      <c r="F1" t="s">
-        <v>266</v>
-      </c>
-      <c r="G1" t="s">
-        <v>267</v>
-      </c>
-      <c r="H1" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>269</v>
-      </c>
-      <c r="C2" t="s">
-        <v>270</v>
-      </c>
-      <c r="D2" t="s">
-        <v>271</v>
-      </c>
-      <c r="E2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" t="s">
-        <v>272</v>
-      </c>
-      <c r="G2" t="s">
-        <v>272</v>
-      </c>
-      <c r="H2" t="s">
-        <v>260</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="2" width="15" customWidth="1"/>
-    <col min="3" max="3" width="20" customWidth="1"/>
-    <col min="4" max="5" width="15" customWidth="1"/>
-    <col min="6" max="6" width="30" customWidth="1"/>
-    <col min="7" max="8" width="15" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>261</v>
-      </c>
-      <c r="B1" t="s">
-        <v>262</v>
-      </c>
-      <c r="C1" t="s">
-        <v>263</v>
-      </c>
-      <c r="D1" t="s">
-        <v>264</v>
-      </c>
-      <c r="E1" t="s">
-        <v>265</v>
-      </c>
-      <c r="F1" t="s">
-        <v>266</v>
-      </c>
-      <c r="G1" t="s">
-        <v>267</v>
-      </c>
-      <c r="H1" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>269</v>
-      </c>
-      <c r="C2" t="s">
-        <v>272</v>
-      </c>
-      <c r="D2" t="s">
-        <v>273</v>
-      </c>
-      <c r="E2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" t="s">
-        <v>272</v>
-      </c>
-      <c r="G2" t="s">
-        <v>272</v>
-      </c>
-      <c r="H2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/expenses.xlsx
+++ b/expenses.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11940"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040"/>
   </bookViews>
   <sheets>
-    <sheet name="Expenses" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Expenses" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
@@ -802,11 +802,11 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1112,9 +1112,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H190"/>
-  <sheetFormatPr defaultRowHeight="0" customHeight="1" zeroHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="0" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1140,7 +1140,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1163,7 +1163,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1186,7 +1186,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1209,7 +1209,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1232,7 +1232,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1255,7 +1255,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1278,7 +1278,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1301,7 +1301,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1324,7 +1324,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1347,7 +1347,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1370,7 +1370,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1393,7 +1393,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1416,7 +1416,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1439,7 +1439,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1462,7 +1462,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1485,7 +1485,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1508,7 +1508,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1531,7 +1531,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1554,7 +1554,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1577,7 +1577,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1600,7 +1600,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1623,7 +1623,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1646,7 +1646,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
@@ -1669,7 +1669,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
@@ -1692,7 +1692,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
@@ -1715,7 +1715,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
@@ -1738,7 +1738,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
@@ -1761,7 +1761,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
@@ -1784,7 +1784,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
@@ -1807,7 +1807,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
@@ -1830,7 +1830,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
@@ -1853,7 +1853,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
@@ -1876,7 +1876,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
@@ -1899,7 +1899,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
@@ -1922,7 +1922,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>35</v>
       </c>
@@ -1945,7 +1945,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
@@ -1968,7 +1968,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>37</v>
       </c>
@@ -1991,7 +1991,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>38</v>
       </c>
@@ -2014,7 +2014,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>39</v>
       </c>
@@ -2037,7 +2037,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>40</v>
       </c>
@@ -2060,7 +2060,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>41</v>
       </c>
@@ -2083,7 +2083,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>42</v>
       </c>
@@ -2106,7 +2106,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>43</v>
       </c>
@@ -2129,7 +2129,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>44</v>
       </c>
@@ -2152,7 +2152,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>45</v>
       </c>
@@ -2175,7 +2175,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>46</v>
       </c>
@@ -2198,7 +2198,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>47</v>
       </c>
@@ -2221,7 +2221,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>48</v>
       </c>
@@ -2244,7 +2244,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>49</v>
       </c>
@@ -2267,7 +2267,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="51" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>50</v>
       </c>
@@ -2290,7 +2290,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="52" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>51</v>
       </c>
@@ -2313,7 +2313,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>52</v>
       </c>
@@ -2336,7 +2336,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>53</v>
       </c>
@@ -2359,7 +2359,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>54</v>
       </c>
@@ -2382,7 +2382,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="56" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>55</v>
       </c>
@@ -2405,7 +2405,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="57" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>56</v>
       </c>
@@ -2428,7 +2428,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>57</v>
       </c>
@@ -2451,7 +2451,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>58</v>
       </c>
@@ -2474,7 +2474,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>59</v>
       </c>
@@ -2497,7 +2497,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="61" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>60</v>
       </c>
@@ -2520,7 +2520,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>61</v>
       </c>
@@ -2543,7 +2543,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="63" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>62</v>
       </c>
@@ -2566,7 +2566,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>63</v>
       </c>
@@ -2589,7 +2589,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="65" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>64</v>
       </c>
@@ -2612,7 +2612,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="66" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>65</v>
       </c>
@@ -2635,7 +2635,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="67" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>66</v>
       </c>
@@ -2658,7 +2658,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>67</v>
       </c>
@@ -2681,7 +2681,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="69" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>68</v>
       </c>
@@ -2704,7 +2704,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="70" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>69</v>
       </c>
@@ -2727,7 +2727,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="71" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>70</v>
       </c>
@@ -2750,7 +2750,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="72" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>71</v>
       </c>
@@ -2773,7 +2773,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>72</v>
       </c>
@@ -2796,7 +2796,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="74" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>73</v>
       </c>
@@ -2819,7 +2819,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="75" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>74</v>
       </c>
@@ -2842,7 +2842,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="76" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>75</v>
       </c>
@@ -2865,7 +2865,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="77" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>76</v>
       </c>
@@ -2888,7 +2888,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="78" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>77</v>
       </c>
@@ -2911,7 +2911,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="79" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>78</v>
       </c>
@@ -2934,7 +2934,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="80" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>79</v>
       </c>
@@ -2957,7 +2957,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="81" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>80</v>
       </c>
@@ -2980,7 +2980,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="82" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>81</v>
       </c>
@@ -3003,7 +3003,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="83" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>82</v>
       </c>
@@ -3026,7 +3026,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="84" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>83</v>
       </c>
@@ -3049,7 +3049,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="85" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>84</v>
       </c>
@@ -3072,7 +3072,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="86" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>85</v>
       </c>
@@ -3095,7 +3095,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="87" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>86</v>
       </c>
@@ -3118,7 +3118,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="88" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>87</v>
       </c>
@@ -3141,7 +3141,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="89" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>88</v>
       </c>
@@ -3164,7 +3164,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="90" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>89</v>
       </c>
@@ -3187,7 +3187,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="91" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>90</v>
       </c>
@@ -3210,7 +3210,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="92" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>91</v>
       </c>
@@ -3233,7 +3233,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="93" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>92</v>
       </c>
@@ -3256,7 +3256,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="94" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>93</v>
       </c>
@@ -3279,7 +3279,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="95" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>94</v>
       </c>
@@ -3302,7 +3302,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="96" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>95</v>
       </c>
@@ -3325,7 +3325,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="97" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>96</v>
       </c>
@@ -3348,7 +3348,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="98" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>97</v>
       </c>
@@ -3371,7 +3371,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="99" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>98</v>
       </c>
@@ -3394,7 +3394,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="100" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>99</v>
       </c>
@@ -3417,7 +3417,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="101" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>100</v>
       </c>
@@ -3440,7 +3440,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="102" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>101</v>
       </c>
@@ -3463,7 +3463,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="103" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>102</v>
       </c>
@@ -3486,7 +3486,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="104" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>103</v>
       </c>
@@ -3509,7 +3509,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="105" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>104</v>
       </c>
@@ -3532,7 +3532,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="106" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>105</v>
       </c>
@@ -3555,7 +3555,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="107" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>106</v>
       </c>
@@ -3578,7 +3578,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="108" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>107</v>
       </c>
@@ -3601,7 +3601,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="109" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>108</v>
       </c>
@@ -3624,7 +3624,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="110" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>109</v>
       </c>
@@ -3647,7 +3647,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="111" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>110</v>
       </c>
@@ -3670,7 +3670,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="112" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>111</v>
       </c>
@@ -3693,7 +3693,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="113" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>112</v>
       </c>
@@ -3716,7 +3716,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="114" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>113</v>
       </c>
@@ -3739,7 +3739,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="115" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>114</v>
       </c>
@@ -3762,7 +3762,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="116" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>115</v>
       </c>
@@ -3785,7 +3785,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="117" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>116</v>
       </c>
@@ -3808,7 +3808,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="118" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>117</v>
       </c>
@@ -3831,7 +3831,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="119" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>118</v>
       </c>
@@ -3854,7 +3854,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="120" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>119</v>
       </c>
@@ -3877,7 +3877,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="121" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>120</v>
       </c>
@@ -3900,7 +3900,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="122" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>121</v>
       </c>
@@ -3923,7 +3923,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="123" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>122</v>
       </c>
@@ -3946,7 +3946,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="124" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>123</v>
       </c>
@@ -3969,7 +3969,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="125" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>124</v>
       </c>
@@ -3992,7 +3992,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="126" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>125</v>
       </c>
@@ -4015,7 +4015,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="127" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>126</v>
       </c>
@@ -4038,7 +4038,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="128" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>127</v>
       </c>
@@ -4061,7 +4061,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="129" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>128</v>
       </c>
@@ -4084,7 +4084,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="130" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>129</v>
       </c>
@@ -4107,7 +4107,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="131" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>130</v>
       </c>
@@ -4130,7 +4130,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="132" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>131</v>
       </c>
@@ -4153,7 +4153,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="133" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>132</v>
       </c>
@@ -4176,7 +4176,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="134" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>133</v>
       </c>
@@ -4199,7 +4199,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="135" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>134</v>
       </c>
@@ -4222,7 +4222,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="136" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>135</v>
       </c>
@@ -4245,7 +4245,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="137" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>136</v>
       </c>
@@ -4268,7 +4268,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="138" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>137</v>
       </c>
@@ -4291,7 +4291,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="139" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>138</v>
       </c>
@@ -4314,7 +4314,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="140" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>139</v>
       </c>
@@ -4337,7 +4337,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="141" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>140</v>
       </c>
@@ -4360,7 +4360,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="142" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>141</v>
       </c>
@@ -4383,7 +4383,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="143" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>142</v>
       </c>
@@ -4406,7 +4406,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="144" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>143</v>
       </c>
@@ -4429,7 +4429,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="145" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>144</v>
       </c>
@@ -4452,7 +4452,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="146" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>145</v>
       </c>
@@ -4475,7 +4475,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="147" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>146</v>
       </c>
@@ -4498,7 +4498,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="148" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>147</v>
       </c>
@@ -4521,7 +4521,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="149" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>148</v>
       </c>
@@ -4544,7 +4544,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="150" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>149</v>
       </c>
@@ -4567,7 +4567,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="151" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>150</v>
       </c>
@@ -4590,7 +4590,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="152" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>151</v>
       </c>
@@ -4613,7 +4613,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="153" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>152</v>
       </c>
@@ -4627,7 +4627,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="154" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>153</v>
       </c>
@@ -4641,7 +4641,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="155" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>154</v>
       </c>
@@ -4655,7 +4655,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="156" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>155</v>
       </c>
@@ -4669,7 +4669,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="157" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>156</v>
       </c>
@@ -4683,7 +4683,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="158" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A158">
         <v>157</v>
       </c>
@@ -4697,7 +4697,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="159" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>158</v>
       </c>
@@ -4711,7 +4711,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="160" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>159</v>
       </c>
@@ -4725,7 +4725,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="161" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>160</v>
       </c>
@@ -4739,7 +4739,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="162" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>161</v>
       </c>
@@ -4753,7 +4753,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="163" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>162</v>
       </c>
@@ -4767,7 +4767,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="164" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>163</v>
       </c>
@@ -4781,7 +4781,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="165" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>164</v>
       </c>
@@ -4795,7 +4795,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="166" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>165</v>
       </c>
@@ -4809,7 +4809,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="167" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>166</v>
       </c>
@@ -4823,7 +4823,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="168" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>167</v>
       </c>
@@ -4837,7 +4837,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="169" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>168</v>
       </c>
@@ -4851,7 +4851,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="170" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>169</v>
       </c>
@@ -4865,7 +4865,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="171" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>170</v>
       </c>
@@ -4879,7 +4879,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="172" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>171</v>
       </c>
@@ -4893,7 +4893,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="173" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>172</v>
       </c>
@@ -4907,7 +4907,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="174" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>173</v>
       </c>
@@ -4921,7 +4921,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="175" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>174</v>
       </c>
@@ -4935,7 +4935,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="176" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A176">
         <v>175</v>
       </c>
@@ -4949,7 +4949,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="177" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>176</v>
       </c>
@@ -4963,7 +4963,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="178" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A178">
         <v>177</v>
       </c>
@@ -4977,7 +4977,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="179" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>178</v>
       </c>
@@ -4991,7 +4991,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="180" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A180">
         <v>179</v>
       </c>
@@ -5005,7 +5005,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="181" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>180</v>
       </c>
@@ -5019,7 +5019,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="182" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A182">
         <v>181</v>
       </c>
@@ -5033,7 +5033,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="183" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A183">
         <v>182</v>
       </c>
@@ -5047,7 +5047,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="184" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A184">
         <v>183</v>
       </c>
@@ -5061,7 +5061,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="185" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A185">
         <v>184</v>
       </c>
@@ -5075,7 +5075,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="186" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A186">
         <v>185</v>
       </c>
@@ -5089,7 +5089,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="187" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>186</v>
       </c>
@@ -5103,7 +5103,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="188" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A188">
         <v>187</v>
       </c>
@@ -5117,7 +5117,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="189" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A189">
         <v>188</v>
       </c>
@@ -5131,7 +5131,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="190" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A190">
         <v>189</v>
       </c>

--- a/expenses.xlsx
+++ b/expenses.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet sheetId="1" name="Expenses" state="visible" r:id="rId4"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1028" uniqueCount="260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1029" uniqueCount="261">
   <si>
     <t>srNo</t>
   </si>
@@ -50,6 +50,9 @@
   </si>
   <si>
     <t>Cash</t>
+  </si>
+  <si>
+    <t/>
   </si>
   <si>
     <t>Niyaz 29</t>
@@ -1156,11 +1159,14 @@
       <c r="E2" t="s">
         <v>11</v>
       </c>
+      <c r="F2" t="s">
+        <v>12</v>
+      </c>
       <c r="G2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -1174,16 +1180,16 @@
         <v>9</v>
       </c>
       <c r="D3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E3" t="s">
         <v>11</v>
       </c>
       <c r="G3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -1194,19 +1200,19 @@
         <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E4" t="s">
         <v>11</v>
       </c>
       <c r="G4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -1217,19 +1223,19 @@
         <v>8</v>
       </c>
       <c r="C5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E5" t="s">
         <v>11</v>
       </c>
       <c r="G5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -1240,19 +1246,19 @@
         <v>8</v>
       </c>
       <c r="C6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" t="s">
         <v>20</v>
       </c>
-      <c r="D6" t="s">
-        <v>19</v>
-      </c>
       <c r="E6" t="s">
         <v>11</v>
       </c>
       <c r="G6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -1263,19 +1269,19 @@
         <v>8</v>
       </c>
       <c r="C7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E7" t="s">
         <v>11</v>
       </c>
       <c r="G7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -1286,19 +1292,19 @@
         <v>8</v>
       </c>
       <c r="C8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E8" t="s">
         <v>11</v>
       </c>
       <c r="G8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -1306,22 +1312,22 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E9" t="s">
         <v>11</v>
       </c>
       <c r="G9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -1329,22 +1335,22 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" t="s">
+        <v>30</v>
+      </c>
+      <c r="D10" t="s">
+        <v>31</v>
+      </c>
+      <c r="E10" t="s">
+        <v>11</v>
+      </c>
+      <c r="G10" t="s">
         <v>28</v>
       </c>
-      <c r="C10" t="s">
-        <v>29</v>
-      </c>
-      <c r="D10" t="s">
-        <v>30</v>
-      </c>
-      <c r="E10" t="s">
-        <v>11</v>
-      </c>
-      <c r="G10" t="s">
-        <v>27</v>
-      </c>
       <c r="H10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -1352,22 +1358,22 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" t="s">
+        <v>17</v>
+      </c>
+      <c r="D11" t="s">
+        <v>15</v>
+      </c>
+      <c r="E11" t="s">
+        <v>11</v>
+      </c>
+      <c r="G11" t="s">
         <v>28</v>
       </c>
-      <c r="C11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D11" t="s">
-        <v>14</v>
-      </c>
-      <c r="E11" t="s">
-        <v>11</v>
-      </c>
-      <c r="G11" t="s">
-        <v>27</v>
-      </c>
       <c r="H11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -1375,22 +1381,22 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E12" t="s">
         <v>11</v>
       </c>
       <c r="G12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -1398,22 +1404,22 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E13" t="s">
         <v>11</v>
       </c>
       <c r="G13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -1421,22 +1427,22 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C14" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D14" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E14" t="s">
         <v>11</v>
       </c>
       <c r="G14" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H14" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -1444,22 +1450,22 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C15" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D15" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E15" t="s">
         <v>11</v>
       </c>
       <c r="G15" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H15" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -1467,22 +1473,22 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C16" t="s">
+        <v>41</v>
+      </c>
+      <c r="D16" t="s">
         <v>40</v>
       </c>
-      <c r="D16" t="s">
-        <v>39</v>
-      </c>
       <c r="E16" t="s">
         <v>11</v>
       </c>
       <c r="G16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H16" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -1490,22 +1496,22 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
+        <v>42</v>
+      </c>
+      <c r="C17" t="s">
         <v>41</v>
       </c>
-      <c r="C17" t="s">
-        <v>40</v>
-      </c>
       <c r="D17" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E17" t="s">
         <v>11</v>
       </c>
       <c r="G17" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H17" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -1513,22 +1519,22 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C18" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E18" t="s">
         <v>11</v>
       </c>
       <c r="G18" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H18" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -1536,22 +1542,22 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C19" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D19" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E19" t="s">
         <v>11</v>
       </c>
       <c r="G19" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H19" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -1559,22 +1565,22 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C20" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D20" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E20" t="s">
         <v>11</v>
       </c>
       <c r="G20" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H20" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -1582,22 +1588,22 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C21" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D21" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E21" t="s">
         <v>11</v>
       </c>
       <c r="G21" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H21" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -1605,22 +1611,22 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C22" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D22" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E22" t="s">
         <v>11</v>
       </c>
       <c r="G22" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H22" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -1628,22 +1634,22 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
+        <v>57</v>
+      </c>
+      <c r="C23" t="s">
+        <v>58</v>
+      </c>
+      <c r="D23" t="s">
+        <v>59</v>
+      </c>
+      <c r="E23" t="s">
+        <v>11</v>
+      </c>
+      <c r="G23" t="s">
         <v>56</v>
       </c>
-      <c r="C23" t="s">
-        <v>57</v>
-      </c>
-      <c r="D23" t="s">
-        <v>58</v>
-      </c>
-      <c r="E23" t="s">
-        <v>11</v>
-      </c>
-      <c r="G23" t="s">
-        <v>55</v>
-      </c>
       <c r="H23" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -1651,22 +1657,22 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
+        <v>57</v>
+      </c>
+      <c r="C24" t="s">
+        <v>60</v>
+      </c>
+      <c r="D24" t="s">
+        <v>61</v>
+      </c>
+      <c r="E24" t="s">
+        <v>11</v>
+      </c>
+      <c r="G24" t="s">
         <v>56</v>
       </c>
-      <c r="C24" t="s">
-        <v>59</v>
-      </c>
-      <c r="D24" t="s">
-        <v>60</v>
-      </c>
-      <c r="E24" t="s">
-        <v>11</v>
-      </c>
-      <c r="G24" t="s">
-        <v>55</v>
-      </c>
       <c r="H24" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -1674,22 +1680,22 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C25" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D25" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E25" t="s">
         <v>11</v>
       </c>
       <c r="G25" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H25" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -1697,22 +1703,22 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C26" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D26" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E26" t="s">
         <v>11</v>
       </c>
       <c r="G26" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H26" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -1720,22 +1726,22 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C27" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D27" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E27" t="s">
         <v>11</v>
       </c>
       <c r="G27" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H27" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -1743,22 +1749,22 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C28" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D28" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E28" t="s">
         <v>11</v>
       </c>
       <c r="G28" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H28" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -1766,22 +1772,22 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C29" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D29" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E29" t="s">
         <v>11</v>
       </c>
       <c r="G29" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H29" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -1789,22 +1795,22 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C30" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D30" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E30" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G30" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H30" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -1812,22 +1818,22 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C31" t="s">
         <v>9</v>
       </c>
       <c r="D31" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E31" t="s">
         <v>11</v>
       </c>
       <c r="G31" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H31" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -1835,22 +1841,22 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C32" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D32" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E32" t="s">
         <v>11</v>
       </c>
       <c r="G32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H32" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -1858,22 +1864,22 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C33" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D33" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E33" t="s">
         <v>11</v>
       </c>
       <c r="G33" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H33" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -1881,22 +1887,22 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C34" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D34" t="s">
+        <v>83</v>
+      </c>
+      <c r="E34" t="s">
+        <v>11</v>
+      </c>
+      <c r="G34" t="s">
         <v>82</v>
       </c>
-      <c r="E34" t="s">
-        <v>11</v>
-      </c>
-      <c r="G34" t="s">
-        <v>81</v>
-      </c>
       <c r="H34" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -1904,22 +1910,22 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C35" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D35" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E35" t="s">
         <v>11</v>
       </c>
       <c r="G35" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H35" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -1927,22 +1933,22 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C36" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D36" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E36" t="s">
         <v>11</v>
       </c>
       <c r="G36" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H36" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -1950,22 +1956,22 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C37" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D37" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E37" t="s">
         <v>11</v>
       </c>
       <c r="G37" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H37" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -1973,22 +1979,22 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C38" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D38" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E38" t="s">
         <v>11</v>
       </c>
       <c r="G38" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H38" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -1996,22 +2002,22 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C39" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D39" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E39" t="s">
         <v>11</v>
       </c>
       <c r="G39" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H39" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2019,22 +2025,22 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C40" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D40" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E40" t="s">
         <v>11</v>
       </c>
       <c r="G40" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H40" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2042,22 +2048,22 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C41" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D41" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E41" t="s">
         <v>11</v>
       </c>
       <c r="G41" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H41" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2065,22 +2071,22 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C42" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D42" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E42" t="s">
         <v>11</v>
       </c>
       <c r="G42" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H42" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2088,22 +2094,22 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C43" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D43" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E43" t="s">
         <v>11</v>
       </c>
       <c r="G43" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H43" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2111,22 +2117,22 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C44" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D44" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E44" t="s">
         <v>11</v>
       </c>
       <c r="G44" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H44" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2134,22 +2140,22 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C45" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D45" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E45" t="s">
         <v>11</v>
       </c>
       <c r="G45" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H45" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2157,22 +2163,22 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C46" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D46" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E46" t="s">
         <v>11</v>
       </c>
       <c r="G46" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H46" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2180,22 +2186,22 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C47" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D47" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E47" t="s">
         <v>11</v>
       </c>
       <c r="G47" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H47" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="48" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2203,22 +2209,22 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C48" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D48" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E48" t="s">
         <v>11</v>
       </c>
       <c r="G48" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H48" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="49" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2226,22 +2232,22 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C49" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D49" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E49" t="s">
         <v>11</v>
       </c>
       <c r="G49" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H49" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2249,22 +2255,22 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C50" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D50" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E50" t="s">
         <v>11</v>
       </c>
       <c r="G50" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H50" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2272,22 +2278,22 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C51" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D51" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E51" t="s">
         <v>11</v>
       </c>
       <c r="G51" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H51" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="52" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2295,22 +2301,22 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C52" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D52" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E52" t="s">
         <v>11</v>
       </c>
       <c r="G52" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H52" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="53" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2318,22 +2324,22 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C53" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D53" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E53" t="s">
         <v>11</v>
       </c>
       <c r="G53" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H53" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="54" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2341,22 +2347,22 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C54" t="s">
+        <v>113</v>
+      </c>
+      <c r="D54" t="s">
+        <v>114</v>
+      </c>
+      <c r="E54" t="s">
+        <v>11</v>
+      </c>
+      <c r="G54" t="s">
         <v>112</v>
       </c>
-      <c r="D54" t="s">
-        <v>113</v>
-      </c>
-      <c r="E54" t="s">
-        <v>11</v>
-      </c>
-      <c r="G54" t="s">
-        <v>111</v>
-      </c>
       <c r="H54" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="55" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2364,22 +2370,22 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C55" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D55" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E55" t="s">
         <v>11</v>
       </c>
       <c r="G55" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H55" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="56" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2387,22 +2393,22 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C56" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D56" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E56" t="s">
         <v>11</v>
       </c>
       <c r="G56" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H56" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="57" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2410,22 +2416,22 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C57" t="s">
         <v>9</v>
       </c>
       <c r="D57" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E57" t="s">
         <v>11</v>
       </c>
       <c r="G57" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H57" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="58" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2433,22 +2439,22 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C58" t="s">
         <v>9</v>
       </c>
       <c r="D58" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E58" t="s">
         <v>11</v>
       </c>
       <c r="G58" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H58" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="59" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2456,22 +2462,22 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C59" t="s">
+        <v>121</v>
+      </c>
+      <c r="D59" t="s">
+        <v>20</v>
+      </c>
+      <c r="E59" t="s">
+        <v>11</v>
+      </c>
+      <c r="G59" t="s">
         <v>120</v>
       </c>
-      <c r="D59" t="s">
-        <v>19</v>
-      </c>
-      <c r="E59" t="s">
-        <v>11</v>
-      </c>
-      <c r="G59" t="s">
-        <v>119</v>
-      </c>
       <c r="H59" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="60" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2479,22 +2485,22 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C60" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D60" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E60" t="s">
         <v>11</v>
       </c>
       <c r="G60" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H60" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="61" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2502,22 +2508,22 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C61" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D61" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E61" t="s">
         <v>11</v>
       </c>
       <c r="G61" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H61" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="62" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2525,22 +2531,22 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C62" t="s">
+        <v>128</v>
+      </c>
+      <c r="D62" t="s">
+        <v>84</v>
+      </c>
+      <c r="E62" t="s">
+        <v>11</v>
+      </c>
+      <c r="G62" t="s">
         <v>127</v>
       </c>
-      <c r="D62" t="s">
-        <v>83</v>
-      </c>
-      <c r="E62" t="s">
-        <v>11</v>
-      </c>
-      <c r="G62" t="s">
-        <v>126</v>
-      </c>
       <c r="H62" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="63" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2548,22 +2554,22 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C63" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D63" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E63" t="s">
         <v>11</v>
       </c>
       <c r="G63" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H63" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="64" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2571,22 +2577,22 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C64" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D64" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E64" t="s">
         <v>11</v>
       </c>
       <c r="G64" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H64" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="65" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2594,22 +2600,22 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C65" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D65" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E65" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G65" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H65" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="66" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2617,22 +2623,22 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C66" t="s">
+        <v>134</v>
+      </c>
+      <c r="D66" t="s">
+        <v>94</v>
+      </c>
+      <c r="E66" t="s">
         <v>133</v>
       </c>
-      <c r="D66" t="s">
-        <v>93</v>
-      </c>
-      <c r="E66" t="s">
-        <v>132</v>
-      </c>
       <c r="G66" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H66" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="67" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2640,22 +2646,22 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C67" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D67" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E67" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G67" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H67" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="68" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2663,22 +2669,22 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C68" t="s">
         <v>9</v>
       </c>
       <c r="D68" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E68" t="s">
         <v>11</v>
       </c>
       <c r="G68" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H68" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2686,22 +2692,22 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C69" t="s">
         <v>9</v>
       </c>
       <c r="D69" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E69" t="s">
         <v>11</v>
       </c>
       <c r="G69" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H69" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="70" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2709,22 +2715,22 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C70" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D70" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E70" t="s">
         <v>11</v>
       </c>
       <c r="G70" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H70" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="71" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2732,22 +2738,22 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C71" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D71" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E71" t="s">
         <v>11</v>
       </c>
       <c r="G71" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H71" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="72" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2755,22 +2761,22 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C72" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D72" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E72" t="s">
         <v>11</v>
       </c>
       <c r="G72" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H72" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="73" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2778,22 +2784,22 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C73" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D73" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E73" t="s">
         <v>11</v>
       </c>
       <c r="G73" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H73" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="74" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2801,22 +2807,22 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C74" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D74" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E74" t="s">
         <v>11</v>
       </c>
       <c r="G74" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H74" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2824,22 +2830,22 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C75" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D75" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E75" t="s">
         <v>11</v>
       </c>
       <c r="G75" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H75" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="76" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2847,22 +2853,22 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C76" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D76" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E76" t="s">
         <v>11</v>
       </c>
       <c r="G76" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H76" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="77" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2870,22 +2876,22 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C77" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D77" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E77" t="s">
         <v>11</v>
       </c>
       <c r="G77" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H77" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="78" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2893,22 +2899,22 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C78" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D78" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E78" t="s">
         <v>11</v>
       </c>
       <c r="G78" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H78" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="79" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2916,22 +2922,22 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C79" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D79" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E79" t="s">
         <v>11</v>
       </c>
       <c r="G79" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H79" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="80" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2939,22 +2945,22 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C80" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D80" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E80" t="s">
         <v>11</v>
       </c>
       <c r="G80" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H80" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="81" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2962,22 +2968,22 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C81" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D81" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E81" t="s">
         <v>11</v>
       </c>
       <c r="G81" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H81" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="82" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2985,22 +2991,22 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C82" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D82" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E82" t="s">
         <v>11</v>
       </c>
       <c r="G82" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H82" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="83" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3008,22 +3014,22 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C83" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D83" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E83" t="s">
         <v>11</v>
       </c>
       <c r="G83" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H83" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="84" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3031,22 +3037,22 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C84" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D84" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E84" t="s">
         <v>11</v>
       </c>
       <c r="G84" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H84" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="85" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3054,22 +3060,22 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C85" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D85" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E85" t="s">
         <v>11</v>
       </c>
       <c r="G85" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H85" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="86" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3077,22 +3083,22 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C86" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D86" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E86" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G86" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H86" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="87" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3100,22 +3106,22 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C87" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D87" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E87" t="s">
         <v>11</v>
       </c>
       <c r="G87" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H87" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="88" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3123,22 +3129,22 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C88" t="s">
+        <v>167</v>
+      </c>
+      <c r="D88" t="s">
+        <v>45</v>
+      </c>
+      <c r="E88" t="s">
+        <v>11</v>
+      </c>
+      <c r="G88" t="s">
         <v>166</v>
       </c>
-      <c r="D88" t="s">
-        <v>44</v>
-      </c>
-      <c r="E88" t="s">
-        <v>11</v>
-      </c>
-      <c r="G88" t="s">
-        <v>165</v>
-      </c>
       <c r="H88" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="89" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3146,22 +3152,22 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C89" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D89" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E89" t="s">
         <v>11</v>
       </c>
       <c r="G89" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H89" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="90" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3169,22 +3175,22 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C90" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D90" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E90" t="s">
         <v>11</v>
       </c>
       <c r="G90" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H90" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="91" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3192,22 +3198,22 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C91" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D91" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E91" t="s">
         <v>11</v>
       </c>
       <c r="G91" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H91" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="92" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3215,22 +3221,22 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C92" t="s">
+        <v>167</v>
+      </c>
+      <c r="D92" t="s">
+        <v>171</v>
+      </c>
+      <c r="E92" t="s">
+        <v>11</v>
+      </c>
+      <c r="G92" t="s">
         <v>166</v>
       </c>
-      <c r="D92" t="s">
-        <v>170</v>
-      </c>
-      <c r="E92" t="s">
-        <v>11</v>
-      </c>
-      <c r="G92" t="s">
-        <v>165</v>
-      </c>
       <c r="H92" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="93" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3238,22 +3244,22 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C93" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D93" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E93" t="s">
         <v>11</v>
       </c>
       <c r="G93" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H93" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="94" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3261,22 +3267,22 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C94" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D94" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E94" t="s">
         <v>11</v>
       </c>
       <c r="G94" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H94" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="95" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3284,22 +3290,22 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C95" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D95" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E95" t="s">
         <v>11</v>
       </c>
       <c r="G95" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H95" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="96" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3307,22 +3313,22 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C96" t="s">
+        <v>176</v>
+      </c>
+      <c r="D96" t="s">
         <v>175</v>
       </c>
-      <c r="D96" t="s">
-        <v>174</v>
-      </c>
       <c r="E96" t="s">
         <v>11</v>
       </c>
       <c r="G96" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H96" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="97" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3330,22 +3336,22 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C97" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D97" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E97" t="s">
         <v>11</v>
       </c>
       <c r="G97" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H97" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="98" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3353,22 +3359,22 @@
         <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C98" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D98" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E98" t="s">
         <v>11</v>
       </c>
       <c r="G98" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H98" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="99" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3376,22 +3382,22 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C99" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D99" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E99" t="s">
         <v>11</v>
       </c>
       <c r="G99" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H99" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="100" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3399,22 +3405,22 @@
         <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C100" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D100" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E100" t="s">
         <v>11</v>
       </c>
       <c r="G100" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H100" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="101" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3422,22 +3428,22 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C101" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D101" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E101" t="s">
         <v>11</v>
       </c>
       <c r="G101" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H101" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="102" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3445,22 +3451,22 @@
         <v>101</v>
       </c>
       <c r="B102" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C102" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D102" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E102" t="s">
         <v>11</v>
       </c>
       <c r="G102" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H102" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="103" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3468,22 +3474,22 @@
         <v>102</v>
       </c>
       <c r="B103" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C103" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D103" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E103" t="s">
         <v>11</v>
       </c>
       <c r="G103" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H103" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="104" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3491,22 +3497,22 @@
         <v>103</v>
       </c>
       <c r="B104" t="s">
+        <v>190</v>
+      </c>
+      <c r="C104" t="s">
+        <v>191</v>
+      </c>
+      <c r="D104" t="s">
+        <v>192</v>
+      </c>
+      <c r="E104" t="s">
+        <v>11</v>
+      </c>
+      <c r="G104" t="s">
         <v>189</v>
       </c>
-      <c r="C104" t="s">
-        <v>190</v>
-      </c>
-      <c r="D104" t="s">
-        <v>191</v>
-      </c>
-      <c r="E104" t="s">
-        <v>11</v>
-      </c>
-      <c r="G104" t="s">
-        <v>188</v>
-      </c>
       <c r="H104" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="105" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3514,22 +3520,22 @@
         <v>104</v>
       </c>
       <c r="B105" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C105" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D105" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E105" t="s">
         <v>11</v>
       </c>
       <c r="G105" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H105" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="106" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3537,22 +3543,22 @@
         <v>105</v>
       </c>
       <c r="B106" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C106" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D106" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E106" t="s">
         <v>11</v>
       </c>
       <c r="G106" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H106" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="107" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3560,22 +3566,22 @@
         <v>106</v>
       </c>
       <c r="B107" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C107" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D107" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E107" t="s">
         <v>11</v>
       </c>
       <c r="G107" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H107" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="108" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3583,22 +3589,22 @@
         <v>107</v>
       </c>
       <c r="B108" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C108" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D108" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E108" t="s">
         <v>11</v>
       </c>
       <c r="G108" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H108" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="109" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3606,22 +3612,22 @@
         <v>108</v>
       </c>
       <c r="B109" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C109" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D109" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E109" t="s">
         <v>11</v>
       </c>
       <c r="G109" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H109" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="110" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3629,22 +3635,22 @@
         <v>109</v>
       </c>
       <c r="B110" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C110" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D110" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E110" t="s">
         <v>11</v>
       </c>
       <c r="G110" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H110" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="111" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3652,22 +3658,22 @@
         <v>110</v>
       </c>
       <c r="B111" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C111" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D111" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E111" t="s">
         <v>11</v>
       </c>
       <c r="G111" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H111" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="112" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3675,22 +3681,22 @@
         <v>111</v>
       </c>
       <c r="B112" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C112" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D112" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E112" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G112" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H112" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="113" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3698,22 +3704,22 @@
         <v>112</v>
       </c>
       <c r="B113" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C113" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D113" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E113" t="s">
         <v>11</v>
       </c>
       <c r="G113" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H113" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="114" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3721,22 +3727,22 @@
         <v>113</v>
       </c>
       <c r="B114" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C114" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D114" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E114" t="s">
         <v>11</v>
       </c>
       <c r="G114" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H114" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="115" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3744,22 +3750,22 @@
         <v>114</v>
       </c>
       <c r="B115" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C115" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D115" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E115" t="s">
         <v>11</v>
       </c>
       <c r="G115" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H115" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="116" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3767,22 +3773,22 @@
         <v>115</v>
       </c>
       <c r="B116" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C116" t="s">
+        <v>212</v>
+      </c>
+      <c r="D116" t="s">
+        <v>213</v>
+      </c>
+      <c r="E116" t="s">
+        <v>11</v>
+      </c>
+      <c r="G116" t="s">
         <v>211</v>
       </c>
-      <c r="D116" t="s">
-        <v>212</v>
-      </c>
-      <c r="E116" t="s">
-        <v>11</v>
-      </c>
-      <c r="G116" t="s">
-        <v>210</v>
-      </c>
       <c r="H116" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="117" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3790,22 +3796,22 @@
         <v>116</v>
       </c>
       <c r="B117" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C117" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D117" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E117" t="s">
         <v>11</v>
       </c>
       <c r="G117" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H117" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="118" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3813,22 +3819,22 @@
         <v>117</v>
       </c>
       <c r="B118" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C118" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D118" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E118" t="s">
         <v>11</v>
       </c>
       <c r="G118" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H118" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="119" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3836,22 +3842,22 @@
         <v>118</v>
       </c>
       <c r="B119" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C119" t="s">
         <v>9</v>
       </c>
       <c r="D119" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E119" t="s">
         <v>11</v>
       </c>
       <c r="G119" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H119" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="120" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3859,22 +3865,22 @@
         <v>119</v>
       </c>
       <c r="B120" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C120" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D120" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E120" t="s">
         <v>11</v>
       </c>
       <c r="G120" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H120" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="121" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3882,22 +3888,22 @@
         <v>120</v>
       </c>
       <c r="B121" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C121" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D121" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E121" t="s">
         <v>11</v>
       </c>
       <c r="G121" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H121" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="122" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3905,22 +3911,22 @@
         <v>121</v>
       </c>
       <c r="B122" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C122" t="s">
         <v>9</v>
       </c>
       <c r="D122" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E122" t="s">
         <v>11</v>
       </c>
       <c r="G122" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H122" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="123" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3928,22 +3934,22 @@
         <v>122</v>
       </c>
       <c r="B123" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C123" t="s">
         <v>9</v>
       </c>
       <c r="D123" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E123" t="s">
         <v>11</v>
       </c>
       <c r="G123" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H123" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="124" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3951,22 +3957,22 @@
         <v>123</v>
       </c>
       <c r="B124" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C124" t="s">
         <v>9</v>
       </c>
       <c r="D124" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E124" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G124" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H124" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="125" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3974,22 +3980,22 @@
         <v>124</v>
       </c>
       <c r="B125" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C125" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D125" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E125" t="s">
         <v>11</v>
       </c>
       <c r="G125" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H125" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="126" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3997,22 +4003,22 @@
         <v>125</v>
       </c>
       <c r="B126" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C126" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D126" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E126" t="s">
         <v>11</v>
       </c>
       <c r="G126" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H126" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="127" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4020,22 +4026,22 @@
         <v>126</v>
       </c>
       <c r="B127" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C127" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D127" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E127" t="s">
         <v>11</v>
       </c>
       <c r="G127" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H127" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="128" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4043,22 +4049,22 @@
         <v>127</v>
       </c>
       <c r="B128" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C128" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D128" t="s">
+        <v>231</v>
+      </c>
+      <c r="E128" t="s">
+        <v>11</v>
+      </c>
+      <c r="G128" t="s">
         <v>230</v>
       </c>
-      <c r="E128" t="s">
-        <v>11</v>
-      </c>
-      <c r="G128" t="s">
-        <v>229</v>
-      </c>
       <c r="H128" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="129" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4066,22 +4072,22 @@
         <v>128</v>
       </c>
       <c r="B129" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C129" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D129" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E129" t="s">
         <v>11</v>
       </c>
       <c r="G129" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H129" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="130" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4089,22 +4095,22 @@
         <v>129</v>
       </c>
       <c r="B130" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C130" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D130" t="s">
+        <v>234</v>
+      </c>
+      <c r="E130" t="s">
+        <v>11</v>
+      </c>
+      <c r="G130" t="s">
         <v>233</v>
       </c>
-      <c r="E130" t="s">
-        <v>11</v>
-      </c>
-      <c r="G130" t="s">
-        <v>232</v>
-      </c>
       <c r="H130" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="131" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4112,22 +4118,22 @@
         <v>130</v>
       </c>
       <c r="B131" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C131" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D131" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E131" t="s">
         <v>11</v>
       </c>
       <c r="G131" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H131" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="132" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4135,22 +4141,22 @@
         <v>131</v>
       </c>
       <c r="B132" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C132" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D132" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E132" t="s">
         <v>11</v>
       </c>
       <c r="G132" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H132" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="133" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4158,22 +4164,22 @@
         <v>132</v>
       </c>
       <c r="B133" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C133" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D133" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E133" t="s">
         <v>11</v>
       </c>
       <c r="G133" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H133" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="134" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4181,22 +4187,22 @@
         <v>133</v>
       </c>
       <c r="B134" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C134" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D134" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E134" t="s">
         <v>11</v>
       </c>
       <c r="G134" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H134" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="135" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4204,22 +4210,22 @@
         <v>134</v>
       </c>
       <c r="B135" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C135" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D135" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E135" t="s">
         <v>11</v>
       </c>
       <c r="G135" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H135" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="136" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4227,22 +4233,22 @@
         <v>135</v>
       </c>
       <c r="B136" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C136" t="s">
         <v>9</v>
       </c>
       <c r="D136" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E136" t="s">
         <v>11</v>
       </c>
       <c r="G136" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H136" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="137" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4250,22 +4256,22 @@
         <v>136</v>
       </c>
       <c r="B137" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C137" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D137" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E137" t="s">
         <v>11</v>
       </c>
       <c r="G137" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H137" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="138" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4273,22 +4279,22 @@
         <v>137</v>
       </c>
       <c r="B138" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C138" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D138" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E138" t="s">
         <v>11</v>
       </c>
       <c r="G138" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H138" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="139" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4296,22 +4302,22 @@
         <v>138</v>
       </c>
       <c r="B139" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C139" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D139" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E139" t="s">
         <v>11</v>
       </c>
       <c r="G139" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H139" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="140" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4319,22 +4325,22 @@
         <v>139</v>
       </c>
       <c r="B140" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C140" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D140" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E140" t="s">
         <v>11</v>
       </c>
       <c r="G140" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H140" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="141" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4342,22 +4348,22 @@
         <v>140</v>
       </c>
       <c r="B141" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C141" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D141" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E141" t="s">
         <v>11</v>
       </c>
       <c r="G141" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H141" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="142" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4365,22 +4371,22 @@
         <v>141</v>
       </c>
       <c r="B142" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C142" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D142" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E142" t="s">
         <v>11</v>
       </c>
       <c r="G142" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H142" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="143" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4388,22 +4394,22 @@
         <v>142</v>
       </c>
       <c r="B143" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C143" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D143" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E143" t="s">
         <v>11</v>
       </c>
       <c r="G143" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H143" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="144" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4411,22 +4417,22 @@
         <v>143</v>
       </c>
       <c r="B144" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C144" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D144" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E144" t="s">
         <v>11</v>
       </c>
       <c r="G144" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H144" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="145" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4434,22 +4440,22 @@
         <v>144</v>
       </c>
       <c r="B145" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C145" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D145" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E145" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G145" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H145" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="146" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4457,22 +4463,22 @@
         <v>145</v>
       </c>
       <c r="B146" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C146" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D146" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E146" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G146" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H146" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="147" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4480,22 +4486,22 @@
         <v>146</v>
       </c>
       <c r="B147" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C147" t="s">
+        <v>134</v>
+      </c>
+      <c r="D147" t="s">
+        <v>185</v>
+      </c>
+      <c r="E147" t="s">
         <v>133</v>
       </c>
-      <c r="D147" t="s">
-        <v>184</v>
-      </c>
-      <c r="E147" t="s">
-        <v>132</v>
-      </c>
       <c r="G147" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H147" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="148" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4503,22 +4509,22 @@
         <v>147</v>
       </c>
       <c r="B148" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C148" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D148" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E148" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G148" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H148" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="149" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4526,22 +4532,22 @@
         <v>148</v>
       </c>
       <c r="B149" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C149" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D149" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E149" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G149" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H149" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="150" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4549,22 +4555,22 @@
         <v>149</v>
       </c>
       <c r="B150" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C150" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D150" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E150" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G150" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H150" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="151" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4572,22 +4578,22 @@
         <v>150</v>
       </c>
       <c r="B151" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C151" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D151" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E151" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G151" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H151" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="152" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4595,22 +4601,22 @@
         <v>151</v>
       </c>
       <c r="B152" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C152" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D152" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E152" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G152" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H152" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="153" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4618,13 +4624,13 @@
         <v>152</v>
       </c>
       <c r="B153" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D153" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H153" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="154" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4632,13 +4638,13 @@
         <v>153</v>
       </c>
       <c r="B154" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D154" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H154" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="155" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4646,13 +4652,13 @@
         <v>154</v>
       </c>
       <c r="B155" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D155" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H155" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="156" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4660,13 +4666,13 @@
         <v>155</v>
       </c>
       <c r="B156" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D156" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H156" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="157" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4674,13 +4680,13 @@
         <v>156</v>
       </c>
       <c r="B157" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D157" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H157" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="158" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4688,13 +4694,13 @@
         <v>157</v>
       </c>
       <c r="B158" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D158" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H158" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="159" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4702,13 +4708,13 @@
         <v>158</v>
       </c>
       <c r="B159" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D159" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H159" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="160" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4716,13 +4722,13 @@
         <v>159</v>
       </c>
       <c r="B160" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D160" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H160" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="161" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4730,13 +4736,13 @@
         <v>160</v>
       </c>
       <c r="B161" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D161" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H161" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="162" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4744,13 +4750,13 @@
         <v>161</v>
       </c>
       <c r="B162" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D162" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H162" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="163" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4758,13 +4764,13 @@
         <v>162</v>
       </c>
       <c r="B163" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D163" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H163" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="164" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4772,13 +4778,13 @@
         <v>163</v>
       </c>
       <c r="B164" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D164" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H164" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="165" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4786,13 +4792,13 @@
         <v>164</v>
       </c>
       <c r="B165" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D165" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H165" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="166" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4800,13 +4806,13 @@
         <v>165</v>
       </c>
       <c r="B166" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D166" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H166" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="167" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4814,13 +4820,13 @@
         <v>166</v>
       </c>
       <c r="B167" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D167" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H167" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="168" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4828,13 +4834,13 @@
         <v>167</v>
       </c>
       <c r="B168" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D168" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H168" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="169" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4842,13 +4848,13 @@
         <v>168</v>
       </c>
       <c r="B169" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D169" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H169" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="170" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4856,13 +4862,13 @@
         <v>169</v>
       </c>
       <c r="B170" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D170" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H170" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="171" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4870,13 +4876,13 @@
         <v>170</v>
       </c>
       <c r="B171" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D171" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H171" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="172" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4884,13 +4890,13 @@
         <v>171</v>
       </c>
       <c r="B172" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D172" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H172" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="173" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4898,13 +4904,13 @@
         <v>172</v>
       </c>
       <c r="B173" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D173" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H173" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="174" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4912,13 +4918,13 @@
         <v>173</v>
       </c>
       <c r="B174" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D174" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H174" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="175" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4926,13 +4932,13 @@
         <v>174</v>
       </c>
       <c r="B175" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D175" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H175" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="176" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4940,13 +4946,13 @@
         <v>175</v>
       </c>
       <c r="B176" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D176" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H176" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="177" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4954,13 +4960,13 @@
         <v>176</v>
       </c>
       <c r="B177" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D177" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H177" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="178" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4968,13 +4974,13 @@
         <v>177</v>
       </c>
       <c r="B178" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D178" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H178" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="179" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4982,13 +4988,13 @@
         <v>178</v>
       </c>
       <c r="B179" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D179" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H179" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="180" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4996,13 +5002,13 @@
         <v>179</v>
       </c>
       <c r="B180" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D180" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H180" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="181" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -5010,13 +5016,13 @@
         <v>180</v>
       </c>
       <c r="B181" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D181" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H181" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="182" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -5024,13 +5030,13 @@
         <v>181</v>
       </c>
       <c r="B182" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D182" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H182" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="183" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -5038,13 +5044,13 @@
         <v>182</v>
       </c>
       <c r="B183" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D183" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H183" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="184" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -5052,13 +5058,13 @@
         <v>183</v>
       </c>
       <c r="B184" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D184" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H184" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="185" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -5066,13 +5072,13 @@
         <v>184</v>
       </c>
       <c r="B185" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D185" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H185" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="186" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -5080,13 +5086,13 @@
         <v>185</v>
       </c>
       <c r="B186" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D186" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H186" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="187" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -5094,13 +5100,13 @@
         <v>186</v>
       </c>
       <c r="B187" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D187" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H187" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="188" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -5108,13 +5114,13 @@
         <v>187</v>
       </c>
       <c r="B188" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D188" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H188" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="189" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -5122,13 +5128,13 @@
         <v>188</v>
       </c>
       <c r="B189" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D189" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H189" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="190" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -5136,13 +5142,13 @@
         <v>189</v>
       </c>
       <c r="B190" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D190" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H190" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
   </sheetData>
